--- a/grupos/1EM - Estadisticos 20231.xlsx
+++ b/grupos/1EM - Estadisticos 20231.xlsx
@@ -68,7 +68,7 @@
     <t>BAROJAS RODRIGUEZ ANGEL DANIEL</t>
   </si>
   <si>
-    <t>CARRASCO CHAVEZ HELI AIMME</t>
+    <t>CARRASCO CHAVEZ HELI AIMEE</t>
   </si>
   <si>
     <t>CASTRO DE JESUS AYLIN AMADA</t>
@@ -359,7 +359,7 @@
     <t>LEYLA SARAI</t>
   </si>
   <si>
-    <t>HELI AIMME</t>
+    <t>HELI AIMEE</t>
   </si>
   <si>
     <t>PAOLA</t>

--- a/grupos/1EM - Estadisticos 20231.xlsx
+++ b/grupos/1EM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="119">
   <si>
     <t>Materia</t>
   </si>
@@ -218,24 +218,24 @@
     <t>Duran Amezcua María Angélica</t>
   </si>
   <si>
+    <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
     <t>Herrera Serrano Mayra Iliana</t>
   </si>
   <si>
-    <t>Ochoa Martínez Mayeli</t>
+    <t>Moreno Aroyo Anél</t>
   </si>
   <si>
     <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
-    <t>Moreno Aroyo Anél</t>
+    <t>Velasco Sánchez David</t>
   </si>
   <si>
     <t>Garcia Felix Jose Antonio</t>
   </si>
   <si>
-    <t>Velasco Sánchez David</t>
-  </si>
-  <si>
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
@@ -251,58 +251,64 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>FLORES</t>
+    <t>BAROJAS</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
   </si>
   <si>
     <t>GUTIERREZ</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>MORENO</t>
   </si>
   <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>RUGERIO</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>CARRASCO</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
+    <t>XOTLANIHUA</t>
   </si>
   <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>RUGERIO</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>TENORIO</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>HILARIO</t>
+    <t>SOTO</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>MONTERROSA</t>
+  </si>
+  <si>
+    <t>ZOPIYACTLE</t>
   </si>
   <si>
     <t>PAZ</t>
@@ -311,85 +317,61 @@
     <t>ARCOS</t>
   </si>
   <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
     <t>MANZANO</t>
   </si>
   <si>
+    <t>ACEVEDO</t>
+  </si>
+  <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
-    <t>MONTERROSA</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>MIXCOA</t>
-  </si>
-  <si>
-    <t>TELE</t>
-  </si>
-  <si>
-    <t>SALINAS</t>
-  </si>
-  <si>
     <t>PEREZ</t>
   </si>
   <si>
-    <t>JULIAN DAVID</t>
+    <t>ANGEL DANIEL</t>
+  </si>
+  <si>
+    <t>DIANA ARLET</t>
+  </si>
+  <si>
+    <t>MARITZA</t>
+  </si>
+  <si>
+    <t>PAOLA</t>
+  </si>
+  <si>
+    <t>TATIANA</t>
   </si>
   <si>
     <t>DANIA LIZETH</t>
   </si>
   <si>
+    <t>KENIA PAOLA</t>
+  </si>
+  <si>
     <t>CINTHIA</t>
   </si>
   <si>
+    <t>MARYGELLI</t>
+  </si>
+  <si>
     <t>ANGEL URIEL</t>
   </si>
   <si>
+    <t>KAREN AMERICA</t>
+  </si>
+  <si>
+    <t>AXEL</t>
+  </si>
+  <si>
+    <t>MAGALY</t>
+  </si>
+  <si>
     <t>LEYLA SARAI</t>
-  </si>
-  <si>
-    <t>HELI AIMEE</t>
-  </si>
-  <si>
-    <t>PAOLA</t>
-  </si>
-  <si>
-    <t>ERNESTO</t>
-  </si>
-  <si>
-    <t>KENIA PAOLA</t>
-  </si>
-  <si>
-    <t>MARYGELLI</t>
-  </si>
-  <si>
-    <t>KAREN AMERICA</t>
-  </si>
-  <si>
-    <t>MICHELLE</t>
-  </si>
-  <si>
-    <t>AXEL</t>
-  </si>
-  <si>
-    <t>MAGALY</t>
-  </si>
-  <si>
-    <t>LUZ MARIA</t>
-  </si>
-  <si>
-    <t>VERONICA</t>
   </si>
   <si>
     <t>JOCELYN</t>
@@ -919,19 +901,19 @@
         <v>8</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -961,10 +943,10 @@
         <v>-1</v>
       </c>
       <c r="W4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y4">
         <v>5</v>
@@ -1008,19 +990,19 @@
         <v>10</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1053,16 +1035,16 @@
         <v>9</v>
       </c>
       <c r="X5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y5">
         <v>10</v>
       </c>
       <c r="Z5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB5">
         <v>10</v>
@@ -1097,19 +1079,19 @@
         <v>6</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1139,16 +1121,16 @@
         <v>-1</v>
       </c>
       <c r="W6">
+        <v>8</v>
+      </c>
+      <c r="X6">
         <v>6</v>
       </c>
-      <c r="X6">
-        <v>5</v>
-      </c>
       <c r="Y6">
         <v>5</v>
       </c>
       <c r="Z6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA6">
         <v>5</v>
@@ -1186,19 +1168,19 @@
         <v>8</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1228,19 +1210,19 @@
         <v>-1</v>
       </c>
       <c r="W7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB7">
         <v>10</v>
@@ -1275,19 +1257,19 @@
         <v>10</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1320,7 +1302,7 @@
         <v>10</v>
       </c>
       <c r="X8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y8">
         <v>9</v>
@@ -1364,19 +1346,19 @@
         <v>9</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1409,13 +1391,13 @@
         <v>10</v>
       </c>
       <c r="X9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y9">
         <v>10</v>
       </c>
       <c r="Z9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA9">
         <v>5</v>
@@ -1453,19 +1435,19 @@
         <v>8</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1495,16 +1477,16 @@
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA10">
         <v>6</v>
@@ -1542,19 +1524,19 @@
         <v>6</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1584,10 +1566,10 @@
         <v>-1</v>
       </c>
       <c r="W11">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="X11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y11">
         <v>5</v>
@@ -1631,19 +1613,19 @@
         <v>5</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1673,7 +1655,7 @@
         <v>-1</v>
       </c>
       <c r="W12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X12">
         <v>5</v>
@@ -1682,10 +1664,10 @@
         <v>5</v>
       </c>
       <c r="Z12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB12">
         <v>5</v>
@@ -1720,19 +1702,19 @@
         <v>9</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1762,19 +1744,19 @@
         <v>-1</v>
       </c>
       <c r="W13">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z13">
         <v>8</v>
       </c>
       <c r="AA13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB13">
         <v>9</v>
@@ -1809,19 +1791,19 @@
         <v>8</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1851,10 +1833,10 @@
         <v>-1</v>
       </c>
       <c r="W14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y14">
         <v>9</v>
@@ -1863,7 +1845,7 @@
         <v>9</v>
       </c>
       <c r="AA14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB14">
         <v>9</v>
@@ -1898,19 +1880,19 @@
         <v>10</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1943,16 +1925,16 @@
         <v>9</v>
       </c>
       <c r="X15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z15">
         <v>9</v>
       </c>
       <c r="AA15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB15">
         <v>10</v>
@@ -1987,19 +1969,19 @@
         <v>9</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -2029,19 +2011,19 @@
         <v>-1</v>
       </c>
       <c r="W16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X16">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y16">
         <v>9</v>
       </c>
       <c r="Z16">
+        <v>8</v>
+      </c>
+      <c r="AA16">
         <v>6</v>
-      </c>
-      <c r="AA16">
-        <v>5</v>
       </c>
       <c r="AB16">
         <v>10</v>
@@ -2076,19 +2058,19 @@
         <v>10</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2118,16 +2100,16 @@
         <v>-1</v>
       </c>
       <c r="W17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X17">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y17">
         <v>9</v>
       </c>
       <c r="Z17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA17">
         <v>8</v>
@@ -2165,19 +2147,19 @@
         <v>9</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2210,7 +2192,7 @@
         <v>9</v>
       </c>
       <c r="X18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y18">
         <v>9</v>
@@ -2254,19 +2236,19 @@
         <v>7</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2296,13 +2278,13 @@
         <v>-1</v>
       </c>
       <c r="W19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z19">
         <v>9</v>
@@ -2343,19 +2325,19 @@
         <v>7</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2432,19 +2414,19 @@
         <v>7</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2521,19 +2503,19 @@
         <v>9</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2563,13 +2545,13 @@
         <v>-1</v>
       </c>
       <c r="W22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z22">
         <v>9</v>
@@ -2610,19 +2592,19 @@
         <v>10</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2652,16 +2634,16 @@
         <v>-1</v>
       </c>
       <c r="W23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y23">
         <v>9</v>
       </c>
       <c r="Z23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA23">
         <v>5</v>
@@ -2699,19 +2681,19 @@
         <v>10</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2744,7 +2726,7 @@
         <v>10</v>
       </c>
       <c r="X24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y24">
         <v>10</v>
@@ -2788,19 +2770,19 @@
         <v>5</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2877,19 +2859,19 @@
         <v>9</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2922,13 +2904,13 @@
         <v>10</v>
       </c>
       <c r="X26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y26">
         <v>10</v>
       </c>
       <c r="Z26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA26">
         <v>8</v>
@@ -2966,19 +2948,19 @@
         <v>9</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -3008,13 +2990,13 @@
         <v>-1</v>
       </c>
       <c r="W27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X27">
         <v>8</v>
       </c>
       <c r="Y27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z27">
         <v>10</v>
@@ -3055,19 +3037,19 @@
         <v>8</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -3097,13 +3079,13 @@
         <v>-1</v>
       </c>
       <c r="W28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X28">
         <v>5</v>
       </c>
       <c r="Y28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z28">
         <v>8</v>
@@ -3144,19 +3126,19 @@
         <v>9</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -3189,13 +3171,13 @@
         <v>9</v>
       </c>
       <c r="X29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y29">
         <v>9</v>
       </c>
       <c r="Z29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA29">
         <v>7</v>
@@ -3233,19 +3215,19 @@
         <v>8</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3275,16 +3257,16 @@
         <v>-1</v>
       </c>
       <c r="W30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y30">
         <v>8</v>
       </c>
       <c r="Z30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA30">
         <v>5</v>
@@ -3322,19 +3304,19 @@
         <v>9</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3364,10 +3346,10 @@
         <v>-1</v>
       </c>
       <c r="W31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y31">
         <v>8</v>
@@ -3411,19 +3393,19 @@
         <v>8</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3453,13 +3435,13 @@
         <v>-1</v>
       </c>
       <c r="W32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X32">
+        <v>7</v>
+      </c>
+      <c r="Y32">
         <v>6</v>
-      </c>
-      <c r="Y32">
-        <v>5</v>
       </c>
       <c r="Z32">
         <v>8</v>
@@ -3500,19 +3482,19 @@
         <v>8</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3542,16 +3524,16 @@
         <v>-1</v>
       </c>
       <c r="W33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X33">
         <v>6</v>
       </c>
       <c r="Y33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA33">
         <v>5</v>
@@ -3589,19 +3571,19 @@
         <v>9</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3631,19 +3613,19 @@
         <v>-1</v>
       </c>
       <c r="W34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB34">
         <v>10</v>
@@ -3678,19 +3660,19 @@
         <v>8</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3720,16 +3702,16 @@
         <v>-1</v>
       </c>
       <c r="W35">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA35">
         <v>5</v>
@@ -3767,19 +3749,19 @@
         <v>10</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3809,16 +3791,16 @@
         <v>-1</v>
       </c>
       <c r="W36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X36">
         <v>7</v>
       </c>
       <c r="Y36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA36">
         <v>5</v>
@@ -3856,19 +3838,19 @@
         <v>8</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3898,16 +3880,16 @@
         <v>-1</v>
       </c>
       <c r="W37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X37">
+        <v>8</v>
+      </c>
+      <c r="Y37">
         <v>6</v>
       </c>
-      <c r="Y37">
-        <v>5</v>
-      </c>
       <c r="Z37">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA37">
         <v>5</v>
@@ -3945,19 +3927,19 @@
         <v>9</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -3987,16 +3969,16 @@
         <v>-1</v>
       </c>
       <c r="W38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z38">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA38">
         <v>6</v>
@@ -4034,19 +4016,19 @@
         <v>8</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N39">
         <v>-1</v>
@@ -4076,7 +4058,7 @@
         <v>-1</v>
       </c>
       <c r="W39">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X39">
         <v>5</v>
@@ -4085,7 +4067,7 @@
         <v>5</v>
       </c>
       <c r="Z39">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA39">
         <v>5</v>
@@ -4123,19 +4105,19 @@
         <v>10</v>
       </c>
       <c r="I40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N40">
         <v>-1</v>
@@ -4165,19 +4147,19 @@
         <v>-1</v>
       </c>
       <c r="W40">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X40">
+        <v>8</v>
+      </c>
+      <c r="Y40">
+        <v>8</v>
+      </c>
+      <c r="Z40">
+        <v>10</v>
+      </c>
+      <c r="AA40">
         <v>6</v>
-      </c>
-      <c r="Y40">
-        <v>7</v>
-      </c>
-      <c r="Z40">
-        <v>9</v>
-      </c>
-      <c r="AA40">
-        <v>5</v>
       </c>
       <c r="AB40">
         <v>10</v>
@@ -4212,19 +4194,19 @@
         <v>10</v>
       </c>
       <c r="I41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N41">
         <v>-1</v>
@@ -4254,16 +4236,16 @@
         <v>-1</v>
       </c>
       <c r="W41">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X41">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y41">
         <v>9</v>
       </c>
       <c r="Z41">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA41">
         <v>9</v>
@@ -4301,19 +4283,19 @@
         <v>8</v>
       </c>
       <c r="I42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N42">
         <v>-1</v>
@@ -4343,16 +4325,16 @@
         <v>-1</v>
       </c>
       <c r="W42">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y42">
         <v>8</v>
       </c>
       <c r="Z42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA42">
         <v>5</v>
@@ -4512,10 +4494,10 @@
         <v>100</v>
       </c>
       <c r="I4">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J4">
-        <v>86.7</v>
+        <v>83.3</v>
       </c>
       <c r="K4">
         <v>100</v>
@@ -4533,10 +4515,10 @@
         <v>100</v>
       </c>
       <c r="P4">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="Q4">
-        <v>86.7</v>
+        <v>83.3</v>
       </c>
       <c r="R4">
         <v>100</v>
@@ -4580,13 +4562,13 @@
         <v>95</v>
       </c>
       <c r="I5">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J5">
         <v>100</v>
       </c>
       <c r="K5">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="L5">
         <v>100</v>
@@ -4601,13 +4583,13 @@
         <v>95</v>
       </c>
       <c r="P5">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="Q5">
         <v>100</v>
       </c>
       <c r="R5">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="S5">
         <v>100</v>
@@ -4648,19 +4630,19 @@
         <v>100</v>
       </c>
       <c r="I6">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J6">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="K6">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="L6">
         <v>100</v>
       </c>
       <c r="M6">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N6">
         <v>100</v>
@@ -4669,19 +4651,19 @@
         <v>100</v>
       </c>
       <c r="P6">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="Q6">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="R6">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="S6">
         <v>100</v>
       </c>
       <c r="T6">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="U6">
         <v>100</v>
@@ -4722,10 +4704,10 @@
         <v>100</v>
       </c>
       <c r="K7">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="L7">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="M7">
         <v>100</v>
@@ -4743,10 +4725,10 @@
         <v>100</v>
       </c>
       <c r="R7">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="S7">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="T7">
         <v>100</v>
@@ -4855,10 +4837,10 @@
         <v>100</v>
       </c>
       <c r="J9">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="K9">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="L9">
         <v>100</v>
@@ -4876,10 +4858,10 @@
         <v>100</v>
       </c>
       <c r="Q9">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="R9">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="S9">
         <v>100</v>
@@ -4929,7 +4911,7 @@
         <v>100</v>
       </c>
       <c r="L10">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="M10">
         <v>100</v>
@@ -4950,7 +4932,7 @@
         <v>100</v>
       </c>
       <c r="S10">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="T10">
         <v>100</v>
@@ -4988,13 +4970,13 @@
         <v>100</v>
       </c>
       <c r="I11">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="J11">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K11">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="L11">
         <v>100</v>
@@ -5009,13 +4991,13 @@
         <v>100</v>
       </c>
       <c r="P11">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="Q11">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R11">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="S11">
         <v>100</v>
@@ -5062,13 +5044,13 @@
         <v>100</v>
       </c>
       <c r="K12">
+        <v>85</v>
+      </c>
+      <c r="L12">
+        <v>86.7</v>
+      </c>
+      <c r="M12">
         <v>90</v>
-      </c>
-      <c r="L12">
-        <v>100</v>
-      </c>
-      <c r="M12">
-        <v>80</v>
       </c>
       <c r="N12">
         <v>93.8</v>
@@ -5083,13 +5065,13 @@
         <v>100</v>
       </c>
       <c r="R12">
+        <v>85</v>
+      </c>
+      <c r="S12">
+        <v>86.7</v>
+      </c>
+      <c r="T12">
         <v>90</v>
-      </c>
-      <c r="S12">
-        <v>100</v>
-      </c>
-      <c r="T12">
-        <v>80</v>
       </c>
       <c r="U12">
         <v>93.8</v>
@@ -5124,7 +5106,7 @@
         <v>100</v>
       </c>
       <c r="I13">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J13">
         <v>100</v>
@@ -5133,7 +5115,7 @@
         <v>100</v>
       </c>
       <c r="L13">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="M13">
         <v>100</v>
@@ -5145,7 +5127,7 @@
         <v>100</v>
       </c>
       <c r="P13">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="Q13">
         <v>100</v>
@@ -5154,7 +5136,7 @@
         <v>100</v>
       </c>
       <c r="S13">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="T13">
         <v>100</v>
@@ -5198,7 +5180,7 @@
         <v>100</v>
       </c>
       <c r="K14">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="L14">
         <v>86.7</v>
@@ -5219,7 +5201,7 @@
         <v>100</v>
       </c>
       <c r="R14">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="S14">
         <v>86.7</v>
@@ -5260,34 +5242,34 @@
         <v>100</v>
       </c>
       <c r="I15">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J15">
         <v>100</v>
       </c>
       <c r="K15">
+        <v>97.5</v>
+      </c>
+      <c r="L15">
+        <v>100</v>
+      </c>
+      <c r="M15">
+        <v>100</v>
+      </c>
+      <c r="N15">
+        <v>100</v>
+      </c>
+      <c r="O15">
+        <v>100</v>
+      </c>
+      <c r="P15">
         <v>95</v>
       </c>
-      <c r="L15">
-        <v>100</v>
-      </c>
-      <c r="M15">
-        <v>100</v>
-      </c>
-      <c r="N15">
-        <v>100</v>
-      </c>
-      <c r="O15">
-        <v>100</v>
-      </c>
-      <c r="P15">
-        <v>100</v>
-      </c>
       <c r="Q15">
         <v>100</v>
       </c>
       <c r="R15">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="S15">
         <v>100</v>
@@ -5402,7 +5384,7 @@
         <v>100</v>
       </c>
       <c r="K17">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="L17">
         <v>100</v>
@@ -5423,7 +5405,7 @@
         <v>100</v>
       </c>
       <c r="R17">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="S17">
         <v>100</v>
@@ -5464,13 +5446,13 @@
         <v>100</v>
       </c>
       <c r="I18">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J18">
         <v>100</v>
       </c>
       <c r="K18">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="L18">
         <v>100</v>
@@ -5485,13 +5467,13 @@
         <v>100</v>
       </c>
       <c r="P18">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q18">
         <v>100</v>
       </c>
       <c r="R18">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="S18">
         <v>100</v>
@@ -5535,13 +5517,13 @@
         <v>100</v>
       </c>
       <c r="J19">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="K19">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="L19">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="M19">
         <v>100</v>
@@ -5556,13 +5538,13 @@
         <v>100</v>
       </c>
       <c r="Q19">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="R19">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="S19">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="T19">
         <v>100</v>
@@ -5603,16 +5585,16 @@
         <v>90</v>
       </c>
       <c r="J20">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="K20">
         <v>85</v>
       </c>
       <c r="L20">
-        <v>86.7</v>
+        <v>83.3</v>
       </c>
       <c r="M20">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="N20">
         <v>93.8</v>
@@ -5624,16 +5606,16 @@
         <v>90</v>
       </c>
       <c r="Q20">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R20">
         <v>85</v>
       </c>
       <c r="S20">
-        <v>86.7</v>
+        <v>83.3</v>
       </c>
       <c r="T20">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="U20">
         <v>93.8</v>
@@ -5671,16 +5653,16 @@
         <v>90</v>
       </c>
       <c r="J21">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="K21">
         <v>90</v>
       </c>
       <c r="L21">
-        <v>86.7</v>
+        <v>90</v>
       </c>
       <c r="M21">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="N21">
         <v>93.8</v>
@@ -5692,16 +5674,16 @@
         <v>90</v>
       </c>
       <c r="Q21">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R21">
         <v>90</v>
       </c>
       <c r="S21">
-        <v>86.7</v>
+        <v>90</v>
       </c>
       <c r="T21">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="U21">
         <v>93.8</v>
@@ -5739,10 +5721,10 @@
         <v>100</v>
       </c>
       <c r="J22">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="K22">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="L22">
         <v>100</v>
@@ -5760,10 +5742,10 @@
         <v>100</v>
       </c>
       <c r="Q22">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="R22">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="S22">
         <v>100</v>
@@ -5940,16 +5922,16 @@
         <v>85</v>
       </c>
       <c r="I25">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="J25">
-        <v>100</v>
+        <v>86.7</v>
       </c>
       <c r="K25">
-        <v>45</v>
+        <v>27.5</v>
       </c>
       <c r="L25">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="M25">
         <v>0</v>
@@ -5961,16 +5943,16 @@
         <v>85</v>
       </c>
       <c r="P25">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="Q25">
-        <v>100</v>
+        <v>86.7</v>
       </c>
       <c r="R25">
-        <v>45</v>
+        <v>27.5</v>
       </c>
       <c r="S25">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="T25">
         <v>0</v>
@@ -6011,10 +5993,10 @@
         <v>100</v>
       </c>
       <c r="J26">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="K26">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="L26">
         <v>100</v>
@@ -6032,10 +6014,10 @@
         <v>100</v>
       </c>
       <c r="Q26">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R26">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="S26">
         <v>100</v>
@@ -6079,7 +6061,7 @@
         <v>100</v>
       </c>
       <c r="J27">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="K27">
         <v>100</v>
@@ -6100,7 +6082,7 @@
         <v>100</v>
       </c>
       <c r="Q27">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="R27">
         <v>100</v>
@@ -6144,19 +6126,19 @@
         <v>85</v>
       </c>
       <c r="I28">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J28">
         <v>100</v>
       </c>
       <c r="K28">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="L28">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="N28">
         <v>87.5</v>
@@ -6165,19 +6147,19 @@
         <v>85</v>
       </c>
       <c r="P28">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="Q28">
         <v>100</v>
       </c>
       <c r="R28">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="S28">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="U28">
         <v>87.5</v>
@@ -6212,7 +6194,7 @@
         <v>100</v>
       </c>
       <c r="I29">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J29">
         <v>100</v>
@@ -6221,10 +6203,10 @@
         <v>85</v>
       </c>
       <c r="L29">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="M29">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="N29">
         <v>100</v>
@@ -6233,7 +6215,7 @@
         <v>100</v>
       </c>
       <c r="P29">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="Q29">
         <v>100</v>
@@ -6242,10 +6224,10 @@
         <v>85</v>
       </c>
       <c r="S29">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="T29">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="U29">
         <v>100</v>
@@ -6416,7 +6398,7 @@
         <v>95</v>
       </c>
       <c r="I32">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J32">
         <v>100</v>
@@ -6425,10 +6407,10 @@
         <v>100</v>
       </c>
       <c r="L32">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="M32">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N32">
         <v>87.5</v>
@@ -6437,7 +6419,7 @@
         <v>95</v>
       </c>
       <c r="P32">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="Q32">
         <v>100</v>
@@ -6446,10 +6428,10 @@
         <v>100</v>
       </c>
       <c r="S32">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="T32">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="U32">
         <v>87.5</v>
@@ -6620,7 +6602,7 @@
         <v>100</v>
       </c>
       <c r="I35">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J35">
         <v>100</v>
@@ -6641,7 +6623,7 @@
         <v>100</v>
       </c>
       <c r="P35">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="Q35">
         <v>100</v>
@@ -6762,10 +6744,10 @@
         <v>100</v>
       </c>
       <c r="K37">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="L37">
-        <v>93.3</v>
+        <v>90</v>
       </c>
       <c r="M37">
         <v>100</v>
@@ -6783,10 +6765,10 @@
         <v>100</v>
       </c>
       <c r="R37">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="S37">
-        <v>93.3</v>
+        <v>90</v>
       </c>
       <c r="T37">
         <v>100</v>
@@ -6824,10 +6806,10 @@
         <v>100</v>
       </c>
       <c r="I38">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J38">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="K38">
         <v>95</v>
@@ -6845,10 +6827,10 @@
         <v>100</v>
       </c>
       <c r="P38">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="Q38">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="R38">
         <v>95</v>
@@ -6892,7 +6874,7 @@
         <v>100</v>
       </c>
       <c r="I39">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J39">
         <v>100</v>
@@ -6913,7 +6895,7 @@
         <v>100</v>
       </c>
       <c r="P39">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="Q39">
         <v>100</v>
@@ -7201,19 +7183,19 @@
         <v>39</v>
       </c>
       <c r="D2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E2">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F2" s="2">
-        <v>38.5</v>
+        <v>46.2</v>
       </c>
       <c r="G2" s="2">
-        <v>61.5</v>
+        <v>53.8</v>
       </c>
       <c r="H2">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -7224,7 +7206,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>66</v>
@@ -7233,19 +7215,19 @@
         <v>39</v>
       </c>
       <c r="D3">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E3">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F3" s="2">
-        <v>66.7</v>
+        <v>79.5</v>
       </c>
       <c r="G3" s="2">
-        <v>33.3</v>
+        <v>20.5</v>
       </c>
       <c r="H3">
-        <v>6.3</v>
+        <v>7.7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -7256,7 +7238,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
@@ -7265,16 +7247,16 @@
         <v>39</v>
       </c>
       <c r="D4">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E4">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F4" s="2">
-        <v>66.7</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="G4" s="2">
-        <v>33.3</v>
+        <v>17.9</v>
       </c>
       <c r="H4">
         <v>7.3</v>
@@ -7288,7 +7270,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>68</v>
@@ -7309,7 +7291,7 @@
         <v>7.7</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -7320,7 +7302,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>69</v>
@@ -7329,19 +7311,19 @@
         <v>39</v>
       </c>
       <c r="D6">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6" s="2">
-        <v>92.3</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="G6" s="2">
-        <v>7.7</v>
+        <v>5.1</v>
       </c>
       <c r="H6">
-        <v>9.4</v>
+        <v>8.5</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7352,7 +7334,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
         <v>70</v>
@@ -7373,7 +7355,7 @@
         <v>5.1</v>
       </c>
       <c r="H7">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7384,7 +7366,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
         <v>71</v>
@@ -7393,19 +7375,19 @@
         <v>39</v>
       </c>
       <c r="D8">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2">
-        <v>94.90000000000001</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="G8" s="2">
-        <v>5.1</v>
+        <v>2.6</v>
       </c>
       <c r="H8">
-        <v>8.4</v>
+        <v>8.9</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -7475,7 +7457,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7507,19 +7489,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920124</v>
+        <v>23330051920118</v>
       </c>
       <c r="B2" t="s">
         <v>77</v>
       </c>
       <c r="C2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
         <v>66</v>
@@ -7530,22 +7512,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920124</v>
+        <v>23330051920118</v>
       </c>
       <c r="B3" t="s">
         <v>77</v>
       </c>
       <c r="C3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D3" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -7553,19 +7535,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920133</v>
+        <v>23330051920123</v>
       </c>
       <c r="B4" t="s">
         <v>78</v>
       </c>
       <c r="C4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D4" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
         <v>66</v>
@@ -7576,16 +7558,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920133</v>
+        <v>23330051920123</v>
       </c>
       <c r="B5" t="s">
         <v>78</v>
       </c>
       <c r="C5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D5" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -7599,22 +7581,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920255</v>
+        <v>23330051920139</v>
       </c>
       <c r="B6" t="s">
         <v>79</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D6" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -7622,16 +7604,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920255</v>
+        <v>23330051920139</v>
       </c>
       <c r="B7" t="s">
         <v>79</v>
       </c>
       <c r="C7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D7" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -7645,22 +7627,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920315</v>
+        <v>23330051920121</v>
       </c>
       <c r="B8" t="s">
         <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D8" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -7668,16 +7650,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920315</v>
+        <v>23330051920130</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D9" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -7691,22 +7673,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920146</v>
+        <v>23330051920133</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D10" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -7714,16 +7696,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920146</v>
+        <v>23330051920134</v>
       </c>
       <c r="B11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" t="s">
         <v>81</v>
       </c>
-      <c r="C11" t="s">
-        <v>98</v>
-      </c>
       <c r="D11" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -7737,16 +7719,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920119</v>
+        <v>23330051920255</v>
       </c>
       <c r="B12" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D12" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -7760,16 +7742,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920121</v>
+        <v>23330051920141</v>
       </c>
       <c r="B13" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D13" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -7783,16 +7765,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920127</v>
+        <v>23330051920315</v>
       </c>
       <c r="B14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C14" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D14" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
@@ -7806,16 +7788,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920134</v>
+        <v>23330051920142</v>
       </c>
       <c r="B15" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C15" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="D15" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
@@ -7829,16 +7811,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920141</v>
+        <v>23330051920144</v>
       </c>
       <c r="B16" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C16" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="D16" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
@@ -7852,16 +7834,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920142</v>
+        <v>23330051920145</v>
       </c>
       <c r="B17" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C17" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="D17" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
@@ -7875,16 +7857,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>23330051920143</v>
+        <v>23330051920146</v>
       </c>
       <c r="B18" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C18" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D18" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E18" t="s">
         <v>9</v>
@@ -7898,16 +7880,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>23330051920144</v>
+        <v>23330051920150</v>
       </c>
       <c r="B19" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C19" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="D19" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E19" t="s">
         <v>9</v>
@@ -7916,98 +7898,6 @@
         <v>65</v>
       </c>
       <c r="G19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>23330051920145</v>
-      </c>
-      <c r="B20" t="s">
-        <v>90</v>
-      </c>
-      <c r="C20" t="s">
-        <v>81</v>
-      </c>
-      <c r="D20" t="s">
-        <v>121</v>
-      </c>
-      <c r="E20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" t="s">
-        <v>65</v>
-      </c>
-      <c r="G20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>23330051920147</v>
-      </c>
-      <c r="B21" t="s">
-        <v>91</v>
-      </c>
-      <c r="C21" t="s">
-        <v>105</v>
-      </c>
-      <c r="D21" t="s">
-        <v>122</v>
-      </c>
-      <c r="E21" t="s">
-        <v>6</v>
-      </c>
-      <c r="F21" t="s">
-        <v>66</v>
-      </c>
-      <c r="G21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>23330051920149</v>
-      </c>
-      <c r="B22" t="s">
-        <v>92</v>
-      </c>
-      <c r="C22" t="s">
-        <v>106</v>
-      </c>
-      <c r="D22" t="s">
-        <v>123</v>
-      </c>
-      <c r="E22" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" t="s">
-        <v>65</v>
-      </c>
-      <c r="G22">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>23330051920150</v>
-      </c>
-      <c r="B23" t="s">
-        <v>93</v>
-      </c>
-      <c r="C23" t="s">
-        <v>107</v>
-      </c>
-      <c r="D23" t="s">
-        <v>124</v>
-      </c>
-      <c r="E23" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" t="s">
-        <v>65</v>
-      </c>
-      <c r="G23">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1EM - Estadisticos 20231.xlsx
+++ b/grupos/1EM - Estadisticos 20231.xlsx
@@ -224,10 +224,10 @@
     <t>Herrera Serrano Mayra Iliana</t>
   </si>
   <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
+  </si>
+  <si>
     <t>Moreno Aroyo Anél</t>
-  </si>
-  <si>
-    <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
     <t>Velasco Sánchez David</t>
@@ -916,7 +916,7 @@
         <v>5</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O4">
         <v>-1</v>
@@ -958,7 +958,7 @@
         <v>5</v>
       </c>
       <c r="AB4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC4">
         <v>8</v>
@@ -1005,7 +1005,7 @@
         <v>7</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O5">
         <v>-1</v>
@@ -1094,7 +1094,7 @@
         <v>6</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O6">
         <v>-1</v>
@@ -1136,7 +1136,7 @@
         <v>5</v>
       </c>
       <c r="AB6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC6">
         <v>6</v>
@@ -1183,7 +1183,7 @@
         <v>7</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
         <v>-1</v>
@@ -1272,7 +1272,7 @@
         <v>9</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
         <v>-1</v>
@@ -1361,7 +1361,7 @@
         <v>6</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O9">
         <v>-1</v>
@@ -1450,7 +1450,7 @@
         <v>6</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
         <v>-1</v>
@@ -1539,7 +1539,7 @@
         <v>6</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O11">
         <v>-1</v>
@@ -1581,7 +1581,7 @@
         <v>5</v>
       </c>
       <c r="AB11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC11">
         <v>6</v>
@@ -1628,7 +1628,7 @@
         <v>5</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O12">
         <v>-1</v>
@@ -1717,7 +1717,7 @@
         <v>7</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O13">
         <v>-1</v>
@@ -1759,7 +1759,7 @@
         <v>7</v>
       </c>
       <c r="AB13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC13">
         <v>9</v>
@@ -1806,7 +1806,7 @@
         <v>7</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O14">
         <v>-1</v>
@@ -1895,7 +1895,7 @@
         <v>8</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
         <v>-1</v>
@@ -1984,7 +1984,7 @@
         <v>7</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
         <v>-1</v>
@@ -2073,7 +2073,7 @@
         <v>8</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
         <v>-1</v>
@@ -2162,7 +2162,7 @@
         <v>6</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O18">
         <v>-1</v>
@@ -2251,7 +2251,7 @@
         <v>6</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
         <v>-1</v>
@@ -2340,7 +2340,7 @@
         <v>5</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O20">
         <v>-1</v>
@@ -2382,7 +2382,7 @@
         <v>5</v>
       </c>
       <c r="AB20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC20">
         <v>7</v>
@@ -2429,7 +2429,7 @@
         <v>5</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O21">
         <v>-1</v>
@@ -2471,7 +2471,7 @@
         <v>5</v>
       </c>
       <c r="AB21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC21">
         <v>7</v>
@@ -2518,7 +2518,7 @@
         <v>5</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O22">
         <v>-1</v>
@@ -2560,7 +2560,7 @@
         <v>5</v>
       </c>
       <c r="AB22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC22">
         <v>9</v>
@@ -2607,7 +2607,7 @@
         <v>6</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
         <v>-1</v>
@@ -2696,7 +2696,7 @@
         <v>8</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
         <v>-1</v>
@@ -2785,7 +2785,7 @@
         <v>5</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O25">
         <v>-1</v>
@@ -2874,7 +2874,7 @@
         <v>7</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
         <v>-1</v>
@@ -2963,7 +2963,7 @@
         <v>7</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
         <v>-1</v>
@@ -3052,7 +3052,7 @@
         <v>6</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O28">
         <v>-1</v>
@@ -3141,7 +3141,7 @@
         <v>7</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O29">
         <v>-1</v>
@@ -3230,7 +3230,7 @@
         <v>6</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
         <v>-1</v>
@@ -3319,7 +3319,7 @@
         <v>6</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O31">
         <v>-1</v>
@@ -3408,7 +3408,7 @@
         <v>5</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O32">
         <v>-1</v>
@@ -3497,7 +3497,7 @@
         <v>6</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O33">
         <v>-1</v>
@@ -3586,7 +3586,7 @@
         <v>7</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O34">
         <v>-1</v>
@@ -3675,7 +3675,7 @@
         <v>6</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O35">
         <v>-1</v>
@@ -3764,7 +3764,7 @@
         <v>6</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O36">
         <v>-1</v>
@@ -3853,7 +3853,7 @@
         <v>6</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O37">
         <v>-1</v>
@@ -3942,7 +3942,7 @@
         <v>6</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O38">
         <v>-1</v>
@@ -3984,7 +3984,7 @@
         <v>6</v>
       </c>
       <c r="AB38">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC38">
         <v>9</v>
@@ -4031,7 +4031,7 @@
         <v>6</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O39">
         <v>-1</v>
@@ -4073,7 +4073,7 @@
         <v>5</v>
       </c>
       <c r="AB39">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC39">
         <v>8</v>
@@ -4120,7 +4120,7 @@
         <v>7</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O40">
         <v>-1</v>
@@ -4209,7 +4209,7 @@
         <v>8</v>
       </c>
       <c r="N41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O41">
         <v>-1</v>
@@ -4298,7 +4298,7 @@
         <v>6</v>
       </c>
       <c r="N42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O42">
         <v>-1</v>
@@ -4509,7 +4509,7 @@
         <v>80</v>
       </c>
       <c r="N4">
-        <v>81.3</v>
+        <v>87.5</v>
       </c>
       <c r="O4">
         <v>100</v>
@@ -4530,7 +4530,7 @@
         <v>80</v>
       </c>
       <c r="U4">
-        <v>81.3</v>
+        <v>87.5</v>
       </c>
       <c r="V4">
         <v>100</v>
@@ -4781,7 +4781,7 @@
         <v>100</v>
       </c>
       <c r="N8">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O8">
         <v>100</v>
@@ -4802,7 +4802,7 @@
         <v>100</v>
       </c>
       <c r="U8">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V8">
         <v>100</v>
@@ -5053,7 +5053,7 @@
         <v>90</v>
       </c>
       <c r="N12">
-        <v>93.8</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="O12">
         <v>90</v>
@@ -5074,7 +5074,7 @@
         <v>90</v>
       </c>
       <c r="U12">
-        <v>93.8</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="V12">
         <v>90</v>
@@ -5189,7 +5189,7 @@
         <v>100</v>
       </c>
       <c r="N14">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="O14">
         <v>100</v>
@@ -5210,7 +5210,7 @@
         <v>100</v>
       </c>
       <c r="U14">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="V14">
         <v>100</v>
@@ -5869,7 +5869,7 @@
         <v>100</v>
       </c>
       <c r="N24">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O24">
         <v>100</v>
@@ -5890,7 +5890,7 @@
         <v>100</v>
       </c>
       <c r="U24">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V24">
         <v>100</v>
@@ -5937,7 +5937,7 @@
         <v>0</v>
       </c>
       <c r="N25">
-        <v>25</v>
+        <v>53.1</v>
       </c>
       <c r="O25">
         <v>85</v>
@@ -5958,7 +5958,7 @@
         <v>0</v>
       </c>
       <c r="U25">
-        <v>25</v>
+        <v>53.1</v>
       </c>
       <c r="V25">
         <v>85</v>
@@ -6073,7 +6073,7 @@
         <v>100</v>
       </c>
       <c r="N27">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O27">
         <v>95</v>
@@ -6094,7 +6094,7 @@
         <v>100</v>
       </c>
       <c r="U27">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V27">
         <v>95</v>
@@ -6141,7 +6141,7 @@
         <v>45</v>
       </c>
       <c r="N28">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="O28">
         <v>85</v>
@@ -6162,7 +6162,7 @@
         <v>45</v>
       </c>
       <c r="U28">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="V28">
         <v>85</v>
@@ -6413,7 +6413,7 @@
         <v>95</v>
       </c>
       <c r="N32">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="O32">
         <v>95</v>
@@ -6434,7 +6434,7 @@
         <v>95</v>
       </c>
       <c r="U32">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="V32">
         <v>95</v>
@@ -6753,7 +6753,7 @@
         <v>100</v>
       </c>
       <c r="N37">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="O37">
         <v>85</v>
@@ -6774,7 +6774,7 @@
         <v>100</v>
       </c>
       <c r="U37">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="V37">
         <v>85</v>
@@ -6957,7 +6957,7 @@
         <v>100</v>
       </c>
       <c r="N40">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O40">
         <v>95</v>
@@ -6978,7 +6978,7 @@
         <v>100</v>
       </c>
       <c r="U40">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V40">
         <v>95</v>
@@ -7270,7 +7270,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>68</v>
@@ -7279,19 +7279,19 @@
         <v>39</v>
       </c>
       <c r="D5">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2">
-        <v>92.3</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="G5" s="2">
-        <v>7.7</v>
+        <v>5.1</v>
       </c>
       <c r="H5">
-        <v>9.4</v>
+        <v>8.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -7302,7 +7302,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>69</v>
@@ -7323,7 +7323,7 @@
         <v>5.1</v>
       </c>
       <c r="H6">
-        <v>8.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>

--- a/grupos/1EM - Estadisticos 20231.xlsx
+++ b/grupos/1EM - Estadisticos 20231.xlsx
@@ -919,7 +919,7 @@
         <v>7</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -961,7 +961,7 @@
         <v>6</v>
       </c>
       <c r="AC4">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -1008,7 +1008,7 @@
         <v>10</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -1097,7 +1097,7 @@
         <v>6</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1186,7 +1186,7 @@
         <v>10</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1228,7 +1228,7 @@
         <v>10</v>
       </c>
       <c r="AC7">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -1275,7 +1275,7 @@
         <v>10</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1364,7 +1364,7 @@
         <v>10</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1453,7 +1453,7 @@
         <v>10</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1495,7 +1495,7 @@
         <v>10</v>
       </c>
       <c r="AC10">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1542,7 +1542,7 @@
         <v>5</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1631,7 +1631,7 @@
         <v>5</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1720,7 +1720,7 @@
         <v>10</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1809,7 +1809,7 @@
         <v>9</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1898,7 +1898,7 @@
         <v>10</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -1987,7 +1987,7 @@
         <v>10</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -2029,7 +2029,7 @@
         <v>10</v>
       </c>
       <c r="AC16">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -2076,7 +2076,7 @@
         <v>10</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -2165,7 +2165,7 @@
         <v>10</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2207,7 +2207,7 @@
         <v>10</v>
       </c>
       <c r="AC18">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2254,7 +2254,7 @@
         <v>10</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2296,7 +2296,7 @@
         <v>10</v>
       </c>
       <c r="AC19">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2343,7 +2343,7 @@
         <v>10</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2432,7 +2432,7 @@
         <v>9</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2521,7 +2521,7 @@
         <v>10</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2563,7 +2563,7 @@
         <v>10</v>
       </c>
       <c r="AC22">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2610,7 +2610,7 @@
         <v>10</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2652,7 +2652,7 @@
         <v>10</v>
       </c>
       <c r="AC23">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -2699,7 +2699,7 @@
         <v>10</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2788,7 +2788,7 @@
         <v>5</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2877,7 +2877,7 @@
         <v>10</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -2919,7 +2919,7 @@
         <v>10</v>
       </c>
       <c r="AC26">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -2966,7 +2966,7 @@
         <v>10</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -3055,7 +3055,7 @@
         <v>9</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -3097,7 +3097,7 @@
         <v>10</v>
       </c>
       <c r="AC28">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -3144,7 +3144,7 @@
         <v>10</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -3233,7 +3233,7 @@
         <v>10</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -3275,7 +3275,7 @@
         <v>10</v>
       </c>
       <c r="AC30">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -3322,7 +3322,7 @@
         <v>9</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P31">
         <v>-1</v>
@@ -3411,7 +3411,7 @@
         <v>9</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P32">
         <v>-1</v>
@@ -3500,7 +3500,7 @@
         <v>9</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P33">
         <v>-1</v>
@@ -3542,7 +3542,7 @@
         <v>10</v>
       </c>
       <c r="AC33">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:29">
@@ -3589,7 +3589,7 @@
         <v>10</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P34">
         <v>-1</v>
@@ -3678,7 +3678,7 @@
         <v>8</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P35">
         <v>-1</v>
@@ -3720,7 +3720,7 @@
         <v>9</v>
       </c>
       <c r="AC35">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:29">
@@ -3767,7 +3767,7 @@
         <v>10</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P36">
         <v>-1</v>
@@ -3809,7 +3809,7 @@
         <v>10</v>
       </c>
       <c r="AC36">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:29">
@@ -3856,7 +3856,7 @@
         <v>10</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P37">
         <v>-1</v>
@@ -3945,7 +3945,7 @@
         <v>5</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P38">
         <v>-1</v>
@@ -4034,7 +4034,7 @@
         <v>6</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P39">
         <v>-1</v>
@@ -4076,7 +4076,7 @@
         <v>8</v>
       </c>
       <c r="AC39">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40" spans="1:29">
@@ -4123,7 +4123,7 @@
         <v>10</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P40">
         <v>-1</v>
@@ -4212,7 +4212,7 @@
         <v>10</v>
       </c>
       <c r="O41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P41">
         <v>-1</v>
@@ -4301,7 +4301,7 @@
         <v>9</v>
       </c>
       <c r="O42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P42">
         <v>-1</v>
@@ -4580,7 +4580,7 @@
         <v>100</v>
       </c>
       <c r="O5">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="P5">
         <v>95</v>
@@ -4601,7 +4601,7 @@
         <v>100</v>
       </c>
       <c r="V5">
-        <v>95</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -4648,7 +4648,7 @@
         <v>100</v>
       </c>
       <c r="O6">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="P6">
         <v>90</v>
@@ -4669,7 +4669,7 @@
         <v>100</v>
       </c>
       <c r="V6">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -4852,7 +4852,7 @@
         <v>100</v>
       </c>
       <c r="O9">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="P9">
         <v>100</v>
@@ -4873,7 +4873,7 @@
         <v>100</v>
       </c>
       <c r="V9">
-        <v>95</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -4988,7 +4988,7 @@
         <v>100</v>
       </c>
       <c r="O11">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P11">
         <v>70</v>
@@ -5009,7 +5009,7 @@
         <v>100</v>
       </c>
       <c r="V11">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -5056,7 +5056,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="O12">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="P12">
         <v>80</v>
@@ -5077,7 +5077,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="V12">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -5192,7 +5192,7 @@
         <v>93.8</v>
       </c>
       <c r="O14">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="P14">
         <v>100</v>
@@ -5213,7 +5213,7 @@
         <v>93.8</v>
       </c>
       <c r="V14">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -5532,7 +5532,7 @@
         <v>100</v>
       </c>
       <c r="O19">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="P19">
         <v>100</v>
@@ -5553,7 +5553,7 @@
         <v>100</v>
       </c>
       <c r="V19">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -5600,7 +5600,7 @@
         <v>93.8</v>
       </c>
       <c r="O20">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P20">
         <v>90</v>
@@ -5621,7 +5621,7 @@
         <v>93.8</v>
       </c>
       <c r="V20">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -5668,7 +5668,7 @@
         <v>93.8</v>
       </c>
       <c r="O21">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P21">
         <v>90</v>
@@ -5689,7 +5689,7 @@
         <v>93.8</v>
       </c>
       <c r="V21">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -5940,7 +5940,7 @@
         <v>53.1</v>
       </c>
       <c r="O25">
-        <v>85</v>
+        <v>62.5</v>
       </c>
       <c r="P25">
         <v>50</v>
@@ -5961,7 +5961,7 @@
         <v>53.1</v>
       </c>
       <c r="V25">
-        <v>85</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -6008,7 +6008,7 @@
         <v>93.8</v>
       </c>
       <c r="O26">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="P26">
         <v>100</v>
@@ -6029,7 +6029,7 @@
         <v>93.8</v>
       </c>
       <c r="V26">
-        <v>95</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -6076,7 +6076,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="O27">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="P27">
         <v>100</v>
@@ -6097,7 +6097,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="V27">
-        <v>95</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -6144,7 +6144,7 @@
         <v>93.8</v>
       </c>
       <c r="O28">
-        <v>85</v>
+        <v>82.5</v>
       </c>
       <c r="P28">
         <v>95</v>
@@ -6165,7 +6165,7 @@
         <v>93.8</v>
       </c>
       <c r="V28">
-        <v>85</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -6212,7 +6212,7 @@
         <v>100</v>
       </c>
       <c r="O29">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="P29">
         <v>95</v>
@@ -6233,7 +6233,7 @@
         <v>100</v>
       </c>
       <c r="V29">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -6280,7 +6280,7 @@
         <v>100</v>
       </c>
       <c r="O30">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="P30">
         <v>100</v>
@@ -6301,7 +6301,7 @@
         <v>100</v>
       </c>
       <c r="V30">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -6416,7 +6416,7 @@
         <v>93.8</v>
       </c>
       <c r="O32">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="P32">
         <v>95</v>
@@ -6437,7 +6437,7 @@
         <v>93.8</v>
       </c>
       <c r="V32">
-        <v>95</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="33" spans="1:22">
@@ -6484,7 +6484,7 @@
         <v>100</v>
       </c>
       <c r="O33">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="P33">
         <v>100</v>
@@ -6505,7 +6505,7 @@
         <v>100</v>
       </c>
       <c r="V33">
-        <v>95</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="34" spans="1:22">
@@ -6552,7 +6552,7 @@
         <v>100</v>
       </c>
       <c r="O34">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="P34">
         <v>100</v>
@@ -6573,7 +6573,7 @@
         <v>100</v>
       </c>
       <c r="V34">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="35" spans="1:22">
@@ -6756,7 +6756,7 @@
         <v>93.8</v>
       </c>
       <c r="O37">
-        <v>85</v>
+        <v>82.5</v>
       </c>
       <c r="P37">
         <v>100</v>
@@ -6777,7 +6777,7 @@
         <v>93.8</v>
       </c>
       <c r="V37">
-        <v>85</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="38" spans="1:22">
@@ -6824,7 +6824,7 @@
         <v>100</v>
       </c>
       <c r="O38">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="P38">
         <v>95</v>
@@ -6845,7 +6845,7 @@
         <v>100</v>
       </c>
       <c r="V38">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="39" spans="1:22">
@@ -6892,7 +6892,7 @@
         <v>100</v>
       </c>
       <c r="O39">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="P39">
         <v>95</v>
@@ -6913,7 +6913,7 @@
         <v>100</v>
       </c>
       <c r="V39">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="40" spans="1:22">
@@ -6960,7 +6960,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="O40">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="P40">
         <v>100</v>
@@ -6981,7 +6981,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="V40">
-        <v>95</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="41" spans="1:22">

--- a/grupos/1EM - Estadisticos 20231.xlsx
+++ b/grupos/1EM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="86">
   <si>
     <t>Materia</t>
   </si>
@@ -224,18 +224,18 @@
     <t>Herrera Serrano Mayra Iliana</t>
   </si>
   <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
+    <t>Garcia Felix Jose Antonio</t>
+  </si>
+  <si>
     <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
     <t>Moreno Aroyo Anél</t>
   </si>
   <si>
-    <t>Velasco Sánchez David</t>
-  </si>
-  <si>
-    <t>Garcia Felix Jose Antonio</t>
-  </si>
-  <si>
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
@@ -251,130 +251,31 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>BAROJAS</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
+    <t>GUTIERREZ</t>
   </si>
   <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>RUGERIO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>SOTO</t>
+    <t>PAZ</t>
   </si>
   <si>
     <t>ORTIZ</t>
   </si>
   <si>
-    <t>MONTERROSA</t>
-  </si>
-  <si>
-    <t>ZOPIYACTLE</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>ARCOS</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
     <t>MANZANO</t>
   </si>
   <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>ANGEL DANIEL</t>
-  </si>
-  <si>
-    <t>DIANA ARLET</t>
+    <t>DANIA LIZETH</t>
   </si>
   <si>
     <t>MARITZA</t>
   </si>
   <si>
-    <t>PAOLA</t>
-  </si>
-  <si>
-    <t>TATIANA</t>
-  </si>
-  <si>
-    <t>DANIA LIZETH</t>
-  </si>
-  <si>
-    <t>KENIA PAOLA</t>
-  </si>
-  <si>
-    <t>CINTHIA</t>
-  </si>
-  <si>
-    <t>MARYGELLI</t>
-  </si>
-  <si>
     <t>ANGEL URIEL</t>
-  </si>
-  <si>
-    <t>KAREN AMERICA</t>
-  </si>
-  <si>
-    <t>AXEL</t>
-  </si>
-  <si>
-    <t>MAGALY</t>
-  </si>
-  <si>
-    <t>LEYLA SARAI</t>
-  </si>
-  <si>
-    <t>JOCELYN</t>
   </si>
 </sst>
 </file>
@@ -922,28 +823,28 @@
         <v>6</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="X4">
         <v>5</v>
@@ -952,7 +853,7 @@
         <v>5</v>
       </c>
       <c r="Z4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA4">
         <v>5</v>
@@ -961,7 +862,7 @@
         <v>6</v>
       </c>
       <c r="AC4">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -1011,25 +912,25 @@
         <v>10</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W5">
         <v>9</v>
@@ -1044,7 +945,7 @@
         <v>9</v>
       </c>
       <c r="AA5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB5">
         <v>10</v>
@@ -1100,28 +1001,28 @@
         <v>6</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X6">
         <v>6</v>
@@ -1139,7 +1040,7 @@
         <v>8</v>
       </c>
       <c r="AC6">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1189,25 +1090,25 @@
         <v>10</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W7">
         <v>10</v>
@@ -1216,13 +1117,13 @@
         <v>8</v>
       </c>
       <c r="Y7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z7">
         <v>10</v>
       </c>
       <c r="AA7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB7">
         <v>10</v>
@@ -1278,25 +1179,25 @@
         <v>10</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W8">
         <v>10</v>
@@ -1367,25 +1268,25 @@
         <v>9</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W9">
         <v>10</v>
@@ -1394,19 +1295,19 @@
         <v>8</v>
       </c>
       <c r="Y9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB9">
         <v>10</v>
       </c>
       <c r="AC9">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1456,25 +1357,25 @@
         <v>9</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W10">
         <v>9</v>
@@ -1483,7 +1384,7 @@
         <v>8</v>
       </c>
       <c r="Y10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z10">
         <v>8</v>
@@ -1545,46 +1446,46 @@
         <v>6</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y11">
         <v>5</v>
       </c>
       <c r="Z11">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AA11">
         <v>5</v>
       </c>
       <c r="AB11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC11">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1634,28 +1535,28 @@
         <v>6</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X12">
         <v>5</v>
@@ -1664,7 +1565,7 @@
         <v>5</v>
       </c>
       <c r="Z12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA12">
         <v>5</v>
@@ -1673,7 +1574,7 @@
         <v>5</v>
       </c>
       <c r="AC12">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1723,28 +1624,28 @@
         <v>9</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X13">
         <v>7</v>
@@ -1756,10 +1657,10 @@
         <v>8</v>
       </c>
       <c r="AA13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC13">
         <v>9</v>
@@ -1812,31 +1713,31 @@
         <v>7</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W14">
         <v>10</v>
       </c>
       <c r="X14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y14">
         <v>9</v>
@@ -1851,7 +1752,7 @@
         <v>9</v>
       </c>
       <c r="AC14">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1901,25 +1802,25 @@
         <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W15">
         <v>9</v>
@@ -1990,34 +1891,34 @@
         <v>10</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W16">
         <v>9</v>
       </c>
       <c r="X16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z16">
         <v>8</v>
@@ -2029,7 +1930,7 @@
         <v>10</v>
       </c>
       <c r="AC16">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -2079,25 +1980,25 @@
         <v>9</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W17">
         <v>10</v>
@@ -2106,19 +2007,19 @@
         <v>8</v>
       </c>
       <c r="Y17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z17">
         <v>10</v>
       </c>
       <c r="AA17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB17">
         <v>10</v>
       </c>
       <c r="AC17">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2168,28 +2069,28 @@
         <v>7</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X18">
         <v>8</v>
@@ -2257,31 +2158,31 @@
         <v>8</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W19">
         <v>9</v>
       </c>
       <c r="X19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y19">
         <v>6</v>
@@ -2290,13 +2191,13 @@
         <v>9</v>
       </c>
       <c r="AA19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC19">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2346,25 +2247,25 @@
         <v>7</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W20">
         <v>7</v>
@@ -2376,16 +2277,16 @@
         <v>5</v>
       </c>
       <c r="Z20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA20">
         <v>5</v>
       </c>
       <c r="AB20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC20">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2435,25 +2336,25 @@
         <v>7</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W21">
         <v>7</v>
@@ -2465,16 +2366,16 @@
         <v>5</v>
       </c>
       <c r="Z21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA21">
         <v>5</v>
       </c>
       <c r="AB21">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC21">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2524,28 +2425,28 @@
         <v>7</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X22">
         <v>6</v>
@@ -2554,13 +2455,13 @@
         <v>7</v>
       </c>
       <c r="Z22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA22">
         <v>5</v>
       </c>
       <c r="AB22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC22">
         <v>8</v>
@@ -2613,40 +2514,40 @@
         <v>8</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y23">
         <v>9</v>
       </c>
       <c r="Z23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB23">
         <v>10</v>
@@ -2702,25 +2603,25 @@
         <v>10</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W24">
         <v>10</v>
@@ -2791,25 +2692,25 @@
         <v>5</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="W25">
         <v>5</v>
@@ -2880,25 +2781,25 @@
         <v>10</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W26">
         <v>10</v>
@@ -2907,10 +2808,10 @@
         <v>8</v>
       </c>
       <c r="Y26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA26">
         <v>8</v>
@@ -2969,25 +2870,25 @@
         <v>9</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W27">
         <v>10</v>
@@ -3058,31 +2959,31 @@
         <v>10</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y28">
         <v>7</v>
@@ -3094,7 +2995,7 @@
         <v>5</v>
       </c>
       <c r="AB28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC28">
         <v>9</v>
@@ -3147,25 +3048,25 @@
         <v>8</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W29">
         <v>9</v>
@@ -3180,13 +3081,13 @@
         <v>10</v>
       </c>
       <c r="AA29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB29">
         <v>10</v>
       </c>
       <c r="AC29">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -3236,25 +3137,25 @@
         <v>9</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W30">
         <v>9</v>
@@ -3266,16 +3167,16 @@
         <v>8</v>
       </c>
       <c r="Z30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB30">
         <v>10</v>
       </c>
       <c r="AC30">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -3325,31 +3226,31 @@
         <v>9</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y31">
         <v>8</v>
@@ -3358,13 +3259,13 @@
         <v>9</v>
       </c>
       <c r="AA31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC31">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:29">
@@ -3414,31 +3315,31 @@
         <v>8</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W32">
         <v>8</v>
       </c>
       <c r="X32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y32">
         <v>6</v>
@@ -3503,28 +3404,28 @@
         <v>6</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X33">
         <v>6</v>
@@ -3533,16 +3434,16 @@
         <v>7</v>
       </c>
       <c r="Z33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC33">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:29">
@@ -3592,40 +3493,40 @@
         <v>9</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y34">
         <v>9</v>
       </c>
       <c r="Z34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB34">
         <v>10</v>
@@ -3681,40 +3582,40 @@
         <v>6</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W35">
         <v>9</v>
       </c>
       <c r="X35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y35">
         <v>7</v>
       </c>
       <c r="Z35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB35">
         <v>9</v>
@@ -3770,46 +3671,46 @@
         <v>8</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W36">
         <v>9</v>
       </c>
       <c r="X36">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y36">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z36">
         <v>9</v>
       </c>
       <c r="AA36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB36">
         <v>10</v>
       </c>
       <c r="AC36">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:29">
@@ -3859,46 +3760,46 @@
         <v>8</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W37">
         <v>9</v>
       </c>
       <c r="X37">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y37">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB37">
         <v>10</v>
       </c>
       <c r="AC37">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:29">
@@ -3948,25 +3849,25 @@
         <v>9</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W38">
         <v>9</v>
@@ -4037,46 +3938,46 @@
         <v>9</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W39">
         <v>8</v>
       </c>
       <c r="X39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z39">
         <v>8</v>
       </c>
       <c r="AA39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB39">
         <v>8</v>
       </c>
       <c r="AC39">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40" spans="1:29">
@@ -4126,25 +4027,25 @@
         <v>9</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W40">
         <v>10</v>
@@ -4156,7 +4057,7 @@
         <v>8</v>
       </c>
       <c r="Z40">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA40">
         <v>6</v>
@@ -4165,7 +4066,7 @@
         <v>10</v>
       </c>
       <c r="AC40">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41" spans="1:29">
@@ -4215,25 +4116,25 @@
         <v>10</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W41">
         <v>10</v>
@@ -4304,25 +4205,25 @@
         <v>7</v>
       </c>
       <c r="P42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W42">
         <v>9</v>
@@ -4337,13 +4238,13 @@
         <v>7</v>
       </c>
       <c r="AA42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB42">
         <v>10</v>
       </c>
       <c r="AC42">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -4515,7 +4416,7 @@
         <v>100</v>
       </c>
       <c r="P4">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="Q4">
         <v>83.3</v>
@@ -4527,10 +4428,10 @@
         <v>100</v>
       </c>
       <c r="T4">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="U4">
-        <v>87.5</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="V4">
         <v>100</v>
@@ -4583,13 +4484,13 @@
         <v>92.5</v>
       </c>
       <c r="P5">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="Q5">
         <v>100</v>
       </c>
       <c r="R5">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S5">
         <v>100</v>
@@ -4601,7 +4502,7 @@
         <v>100</v>
       </c>
       <c r="V5">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -4651,25 +4552,25 @@
         <v>95</v>
       </c>
       <c r="P6">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="Q6">
+        <v>95.8</v>
+      </c>
+      <c r="R6">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="S6">
+        <v>100</v>
+      </c>
+      <c r="T6">
         <v>93.3</v>
       </c>
-      <c r="R6">
-        <v>97.5</v>
-      </c>
-      <c r="S6">
-        <v>100</v>
-      </c>
-      <c r="T6">
-        <v>95</v>
-      </c>
       <c r="U6">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V6">
-        <v>95</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -4725,10 +4626,10 @@
         <v>100</v>
       </c>
       <c r="R7">
-        <v>92.5</v>
+        <v>93.8</v>
       </c>
       <c r="S7">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="T7">
         <v>100</v>
@@ -4793,16 +4694,16 @@
         <v>100</v>
       </c>
       <c r="R8">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S8">
         <v>100</v>
       </c>
       <c r="T8">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="U8">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V8">
         <v>100</v>
@@ -4855,13 +4756,13 @@
         <v>97.5</v>
       </c>
       <c r="P9">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="Q9">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="R9">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S9">
         <v>100</v>
@@ -4870,10 +4771,10 @@
         <v>100</v>
       </c>
       <c r="U9">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V9">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -4932,7 +4833,7 @@
         <v>100</v>
       </c>
       <c r="S10">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="T10">
         <v>100</v>
@@ -4991,25 +4892,25 @@
         <v>90</v>
       </c>
       <c r="P11">
-        <v>70</v>
+        <v>46.7</v>
       </c>
       <c r="Q11">
-        <v>90</v>
+        <v>56.3</v>
       </c>
       <c r="R11">
-        <v>92.5</v>
+        <v>57.8</v>
       </c>
       <c r="S11">
-        <v>100</v>
+        <v>62.5</v>
       </c>
       <c r="T11">
         <v>100</v>
       </c>
       <c r="U11">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="V11">
-        <v>90</v>
+        <v>56.3</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -5065,19 +4966,19 @@
         <v>100</v>
       </c>
       <c r="R12">
-        <v>85</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="S12">
-        <v>86.7</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="T12">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="U12">
-        <v>84.40000000000001</v>
+        <v>60.4</v>
       </c>
       <c r="V12">
-        <v>85</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -5127,7 +5028,7 @@
         <v>100</v>
       </c>
       <c r="P13">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="Q13">
         <v>100</v>
@@ -5136,13 +5037,13 @@
         <v>100</v>
       </c>
       <c r="S13">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="T13">
         <v>100</v>
       </c>
       <c r="U13">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="V13">
         <v>100</v>
@@ -5201,19 +5102,19 @@
         <v>100</v>
       </c>
       <c r="R14">
-        <v>97.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S14">
-        <v>86.7</v>
+        <v>91.7</v>
       </c>
       <c r="T14">
         <v>100</v>
       </c>
       <c r="U14">
-        <v>93.8</v>
+        <v>91.7</v>
       </c>
       <c r="V14">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -5263,13 +5164,13 @@
         <v>100</v>
       </c>
       <c r="P15">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="Q15">
         <v>100</v>
       </c>
       <c r="R15">
-        <v>97.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S15">
         <v>100</v>
@@ -5337,7 +5238,7 @@
         <v>100</v>
       </c>
       <c r="R16">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S16">
         <v>100</v>
@@ -5405,7 +5306,7 @@
         <v>100</v>
       </c>
       <c r="R17">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S17">
         <v>100</v>
@@ -5467,13 +5368,13 @@
         <v>100</v>
       </c>
       <c r="P18">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="Q18">
         <v>100</v>
       </c>
       <c r="R18">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S18">
         <v>100</v>
@@ -5482,7 +5383,7 @@
         <v>100</v>
       </c>
       <c r="U18">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V18">
         <v>100</v>
@@ -5538,22 +5439,22 @@
         <v>100</v>
       </c>
       <c r="Q19">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="R19">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
       <c r="S19">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="T19">
         <v>100</v>
       </c>
       <c r="U19">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V19">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -5603,25 +5504,25 @@
         <v>90</v>
       </c>
       <c r="P20">
+        <v>93.3</v>
+      </c>
+      <c r="Q20">
+        <v>87.5</v>
+      </c>
+      <c r="R20">
+        <v>87.5</v>
+      </c>
+      <c r="S20">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="T20">
         <v>90</v>
       </c>
-      <c r="Q20">
-        <v>90</v>
-      </c>
-      <c r="R20">
-        <v>85</v>
-      </c>
-      <c r="S20">
-        <v>83.3</v>
-      </c>
-      <c r="T20">
-        <v>87.5</v>
-      </c>
       <c r="U20">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="V20">
         <v>93.8</v>
-      </c>
-      <c r="V20">
-        <v>90</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -5671,25 +5572,25 @@
         <v>90</v>
       </c>
       <c r="P21">
+        <v>93.3</v>
+      </c>
+      <c r="Q21">
+        <v>87.5</v>
+      </c>
+      <c r="R21">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="S21">
+        <v>93.8</v>
+      </c>
+      <c r="T21">
         <v>90</v>
       </c>
-      <c r="Q21">
-        <v>90</v>
-      </c>
-      <c r="R21">
-        <v>90</v>
-      </c>
-      <c r="S21">
-        <v>90</v>
-      </c>
-      <c r="T21">
-        <v>87.5</v>
-      </c>
       <c r="U21">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="V21">
         <v>93.8</v>
-      </c>
-      <c r="V21">
-        <v>90</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -5742,19 +5643,19 @@
         <v>100</v>
       </c>
       <c r="Q22">
-        <v>93.3</v>
+        <v>91.7</v>
       </c>
       <c r="R22">
-        <v>97.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S22">
         <v>100</v>
       </c>
       <c r="T22">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="U22">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="V22">
         <v>100</v>
@@ -5807,13 +5708,13 @@
         <v>100</v>
       </c>
       <c r="P23">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="Q23">
         <v>100</v>
       </c>
       <c r="R23">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S23">
         <v>100</v>
@@ -5822,7 +5723,7 @@
         <v>100</v>
       </c>
       <c r="U23">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V23">
         <v>100</v>
@@ -5890,7 +5791,7 @@
         <v>100</v>
       </c>
       <c r="U24">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V24">
         <v>100</v>
@@ -5943,25 +5844,25 @@
         <v>62.5</v>
       </c>
       <c r="P25">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="Q25">
-        <v>86.7</v>
+        <v>54.2</v>
       </c>
       <c r="R25">
-        <v>27.5</v>
+        <v>17.2</v>
       </c>
       <c r="S25">
-        <v>66.7</v>
+        <v>41.7</v>
       </c>
       <c r="T25">
         <v>0</v>
       </c>
       <c r="U25">
-        <v>53.1</v>
+        <v>35.4</v>
       </c>
       <c r="V25">
-        <v>62.5</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -6014,22 +5915,22 @@
         <v>100</v>
       </c>
       <c r="Q26">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="R26">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S26">
         <v>100</v>
       </c>
       <c r="T26">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="U26">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="V26">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -6082,7 +5983,7 @@
         <v>100</v>
       </c>
       <c r="Q27">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="R27">
         <v>100</v>
@@ -6094,10 +5995,10 @@
         <v>100</v>
       </c>
       <c r="U27">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V27">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -6147,25 +6048,25 @@
         <v>82.5</v>
       </c>
       <c r="P28">
-        <v>95</v>
+        <v>93.3</v>
       </c>
       <c r="Q28">
         <v>100</v>
       </c>
       <c r="R28">
-        <v>92.5</v>
+        <v>93.8</v>
       </c>
       <c r="S28">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T28">
-        <v>45</v>
+        <v>63.3</v>
       </c>
       <c r="U28">
-        <v>93.8</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="V28">
-        <v>82.5</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -6215,25 +6116,25 @@
         <v>95</v>
       </c>
       <c r="P29">
-        <v>95</v>
+        <v>93.3</v>
       </c>
       <c r="Q29">
         <v>100</v>
       </c>
       <c r="R29">
-        <v>85</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="S29">
-        <v>96.7</v>
+        <v>95.8</v>
       </c>
       <c r="T29">
-        <v>97.5</v>
+        <v>98.3</v>
       </c>
       <c r="U29">
         <v>100</v>
       </c>
       <c r="V29">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -6298,10 +6199,10 @@
         <v>100</v>
       </c>
       <c r="U30">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V30">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -6351,22 +6252,22 @@
         <v>100</v>
       </c>
       <c r="P31">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="Q31">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="R31">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S31">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T31">
         <v>100</v>
       </c>
       <c r="U31">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="V31">
         <v>100</v>
@@ -6419,25 +6320,25 @@
         <v>97.5</v>
       </c>
       <c r="P32">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="Q32">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R32">
         <v>100</v>
       </c>
       <c r="S32">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="T32">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="U32">
         <v>93.8</v>
       </c>
       <c r="V32">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:22">
@@ -6490,10 +6391,10 @@
         <v>100</v>
       </c>
       <c r="Q33">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R33">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S33">
         <v>100</v>
@@ -6502,10 +6403,10 @@
         <v>100</v>
       </c>
       <c r="U33">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="V33">
-        <v>97.5</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="34" spans="1:22">
@@ -6555,13 +6456,13 @@
         <v>95</v>
       </c>
       <c r="P34">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="Q34">
         <v>100</v>
       </c>
       <c r="R34">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S34">
         <v>100</v>
@@ -6573,7 +6474,7 @@
         <v>100</v>
       </c>
       <c r="V34">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:22">
@@ -6623,7 +6524,7 @@
         <v>100</v>
       </c>
       <c r="P35">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="Q35">
         <v>100</v>
@@ -6638,7 +6539,7 @@
         <v>100</v>
       </c>
       <c r="U35">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V35">
         <v>100</v>
@@ -6762,22 +6663,22 @@
         <v>100</v>
       </c>
       <c r="Q37">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="R37">
-        <v>92.5</v>
+        <v>93.8</v>
       </c>
       <c r="S37">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="T37">
         <v>100</v>
       </c>
       <c r="U37">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="V37">
-        <v>82.5</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="38" spans="1:22">
@@ -6827,13 +6728,13 @@
         <v>95</v>
       </c>
       <c r="P38">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="Q38">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="R38">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S38">
         <v>100</v>
@@ -6845,7 +6746,7 @@
         <v>100</v>
       </c>
       <c r="V38">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="39" spans="1:22">
@@ -6895,7 +6796,7 @@
         <v>95</v>
       </c>
       <c r="P39">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="Q39">
         <v>100</v>
@@ -6910,10 +6811,10 @@
         <v>100</v>
       </c>
       <c r="U39">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V39">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="40" spans="1:22">
@@ -6969,7 +6870,7 @@
         <v>100</v>
       </c>
       <c r="R40">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S40">
         <v>100</v>
@@ -6978,10 +6879,10 @@
         <v>100</v>
       </c>
       <c r="U40">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V40">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="41" spans="1:22">
@@ -7183,19 +7084,19 @@
         <v>39</v>
       </c>
       <c r="D2">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="E2">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F2" s="2">
-        <v>46.2</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="G2" s="2">
-        <v>53.8</v>
+        <v>25.6</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -7215,19 +7116,19 @@
         <v>39</v>
       </c>
       <c r="D3">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F3" s="2">
-        <v>79.5</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="G3" s="2">
-        <v>20.5</v>
+        <v>17.9</v>
       </c>
       <c r="H3">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -7247,19 +7148,19 @@
         <v>39</v>
       </c>
       <c r="D4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F4" s="2">
-        <v>82.09999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="G4" s="2">
-        <v>17.9</v>
+        <v>15.4</v>
       </c>
       <c r="H4">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -7270,7 +7171,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
         <v>68</v>
@@ -7279,19 +7180,19 @@
         <v>39</v>
       </c>
       <c r="D5">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" s="2">
-        <v>94.90000000000001</v>
+        <v>92.3</v>
       </c>
       <c r="G5" s="2">
-        <v>5.1</v>
+        <v>7.7</v>
       </c>
       <c r="H5">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -7302,7 +7203,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>69</v>
@@ -7323,7 +7224,7 @@
         <v>5.1</v>
       </c>
       <c r="H6">
-        <v>9.300000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7334,7 +7235,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>70</v>
@@ -7355,7 +7256,7 @@
         <v>5.1</v>
       </c>
       <c r="H7">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7366,7 +7267,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
         <v>71</v>
@@ -7375,19 +7276,19 @@
         <v>39</v>
       </c>
       <c r="D8">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" s="2">
-        <v>97.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="G8" s="2">
-        <v>2.6</v>
+        <v>5.1</v>
       </c>
       <c r="H8">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -7457,7 +7358,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7489,22 +7390,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920118</v>
+        <v>23330051920133</v>
       </c>
       <c r="B2" t="s">
         <v>77</v>
       </c>
       <c r="C2" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D2" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -7512,16 +7413,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920118</v>
+        <v>23330051920139</v>
       </c>
       <c r="B3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -7535,369 +7436,24 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920123</v>
+        <v>23330051920315</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C4" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="D4" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>23330051920123</v>
-      </c>
-      <c r="B5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C5" t="s">
-        <v>93</v>
-      </c>
-      <c r="D5" t="s">
-        <v>105</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>65</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>23330051920139</v>
-      </c>
-      <c r="B6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C6" t="s">
-        <v>94</v>
-      </c>
-      <c r="D6" t="s">
-        <v>106</v>
-      </c>
-      <c r="E6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" t="s">
-        <v>67</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>23330051920139</v>
-      </c>
-      <c r="B7" t="s">
-        <v>79</v>
-      </c>
-      <c r="C7" t="s">
-        <v>94</v>
-      </c>
-      <c r="D7" t="s">
-        <v>106</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>65</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>23330051920121</v>
-      </c>
-      <c r="B8" t="s">
-        <v>80</v>
-      </c>
-      <c r="C8" t="s">
-        <v>95</v>
-      </c>
-      <c r="D8" t="s">
-        <v>107</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>65</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>23330051920130</v>
-      </c>
-      <c r="B9" t="s">
-        <v>81</v>
-      </c>
-      <c r="C9" t="s">
-        <v>96</v>
-      </c>
-      <c r="D9" t="s">
-        <v>108</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>65</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>23330051920133</v>
-      </c>
-      <c r="B10" t="s">
-        <v>82</v>
-      </c>
-      <c r="C10" t="s">
-        <v>97</v>
-      </c>
-      <c r="D10" t="s">
-        <v>109</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>65</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>23330051920134</v>
-      </c>
-      <c r="B11" t="s">
-        <v>83</v>
-      </c>
-      <c r="C11" t="s">
-        <v>81</v>
-      </c>
-      <c r="D11" t="s">
-        <v>110</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>65</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>23330051920255</v>
-      </c>
-      <c r="B12" t="s">
-        <v>84</v>
-      </c>
-      <c r="C12" t="s">
-        <v>98</v>
-      </c>
-      <c r="D12" t="s">
-        <v>111</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>65</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>23330051920141</v>
-      </c>
-      <c r="B13" t="s">
-        <v>85</v>
-      </c>
-      <c r="C13" t="s">
-        <v>99</v>
-      </c>
-      <c r="D13" t="s">
-        <v>112</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>65</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>23330051920315</v>
-      </c>
-      <c r="B14" t="s">
-        <v>86</v>
-      </c>
-      <c r="C14" t="s">
-        <v>100</v>
-      </c>
-      <c r="D14" t="s">
-        <v>113</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>65</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>23330051920142</v>
-      </c>
-      <c r="B15" t="s">
-        <v>87</v>
-      </c>
-      <c r="C15" t="s">
-        <v>101</v>
-      </c>
-      <c r="D15" t="s">
-        <v>114</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>65</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>23330051920144</v>
-      </c>
-      <c r="B16" t="s">
-        <v>88</v>
-      </c>
-      <c r="C16" t="s">
-        <v>88</v>
-      </c>
-      <c r="D16" t="s">
-        <v>115</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>65</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>23330051920145</v>
-      </c>
-      <c r="B17" t="s">
-        <v>89</v>
-      </c>
-      <c r="C17" t="s">
-        <v>90</v>
-      </c>
-      <c r="D17" t="s">
-        <v>116</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>65</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>23330051920146</v>
-      </c>
-      <c r="B18" t="s">
-        <v>90</v>
-      </c>
-      <c r="C18" t="s">
-        <v>102</v>
-      </c>
-      <c r="D18" t="s">
-        <v>117</v>
-      </c>
-      <c r="E18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" t="s">
-        <v>65</v>
-      </c>
-      <c r="G18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>23330051920150</v>
-      </c>
-      <c r="B19" t="s">
-        <v>91</v>
-      </c>
-      <c r="C19" t="s">
-        <v>103</v>
-      </c>
-      <c r="D19" t="s">
-        <v>118</v>
-      </c>
-      <c r="E19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" t="s">
-        <v>65</v>
-      </c>
-      <c r="G19">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1EM - Estadisticos 20231.xlsx
+++ b/grupos/1EM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="83">
   <si>
     <t>Materia</t>
   </si>
@@ -254,25 +254,16 @@
     <t>GUTIERREZ</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
     <t>PAZ</t>
   </si>
   <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
     <t>MANZANO</t>
   </si>
   <si>
     <t>DANIA LIZETH</t>
-  </si>
-  <si>
-    <t>MARITZA</t>
   </si>
   <si>
     <t>ANGEL URIEL</t>
@@ -2992,7 +2983,7 @@
         <v>8</v>
       </c>
       <c r="AA28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB28">
         <v>9</v>
@@ -4904,7 +4895,7 @@
         <v>62.5</v>
       </c>
       <c r="T11">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="U11">
         <v>93.8</v>
@@ -6018,7 +6009,7 @@
         <v>93.3</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G28">
         <v>87.5</v>
@@ -6039,7 +6030,7 @@
         <v>96.7</v>
       </c>
       <c r="M28">
-        <v>45</v>
+        <v>95</v>
       </c>
       <c r="N28">
         <v>93.8</v>
@@ -6060,7 +6051,7 @@
         <v>97.90000000000001</v>
       </c>
       <c r="T28">
-        <v>63.3</v>
+        <v>96.7</v>
       </c>
       <c r="U28">
         <v>89.59999999999999</v>
@@ -7084,16 +7075,16 @@
         <v>39</v>
       </c>
       <c r="D2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F2" s="2">
-        <v>74.40000000000001</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="G2" s="2">
-        <v>25.6</v>
+        <v>23.1</v>
       </c>
       <c r="H2">
         <v>6.5</v>
@@ -7358,7 +7349,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7396,10 +7387,10 @@
         <v>77</v>
       </c>
       <c r="C2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -7413,16 +7404,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920139</v>
+        <v>23330051920315</v>
       </c>
       <c r="B3" t="s">
         <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -7431,29 +7422,6 @@
         <v>65</v>
       </c>
       <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>23330051920315</v>
-      </c>
-      <c r="B4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D4" t="s">
-        <v>85</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>65</v>
-      </c>
-      <c r="G4">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1EM - Estadisticos 20231.xlsx
+++ b/grupos/1EM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="83">
   <si>
     <t>Materia</t>
   </si>
@@ -54,6 +54,9 @@
   </si>
   <si>
     <t>Pensamiento matemático I</t>
+  </si>
+  <si>
+    <t>Recursos socioemocionales I</t>
   </si>
   <si>
     <t>Nombre</t>
@@ -210,9 +213,6 @@
   </si>
   <si>
     <t>Por_Blancos</t>
-  </si>
-  <si>
-    <t>Recursos socioemocionales I</t>
   </si>
   <si>
     <t>Duran Amezcua María Angélica</t>
@@ -628,13 +628,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC42"/>
+  <dimension ref="A1:AG42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29">
+    <row r="1" spans="1:33">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -645,35 +645,39 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="1"/>
+      <c r="J1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
-      <c r="W1" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="W1" s="1"/>
       <c r="X1" s="1"/>
       <c r="Y1" s="1"/>
-      <c r="Z1" s="1"/>
+      <c r="Z1" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="AA1" s="1"/>
       <c r="AB1" s="1"/>
       <c r="AC1" s="1"/>
-    </row>
-    <row r="2" spans="1:29">
+      <c r="AD1" s="1"/>
+      <c r="AE1" s="1"/>
+      <c r="AF1" s="1"/>
+      <c r="AG1" s="1"/>
+    </row>
+    <row r="2" spans="1:33">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -699,77 +703,89 @@
         <v>11</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="Q2" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="X2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="W2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="Y2" s="1" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF2" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:29">
+      <c r="AG2" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33">
       <c r="A3" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:29">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4">
         <v>5</v>
@@ -796,43 +812,43 @@
         <v>10</v>
       </c>
       <c r="J4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K4">
         <v>5</v>
       </c>
       <c r="L4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P4">
+        <v>6</v>
+      </c>
+      <c r="Q4">
+        <v>10</v>
+      </c>
+      <c r="R4">
         <v>4</v>
       </c>
-      <c r="Q4">
-        <v>5</v>
-      </c>
-      <c r="R4">
-        <v>5</v>
-      </c>
       <c r="S4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W4">
         <v>6</v>
@@ -841,7 +857,7 @@
         <v>5</v>
       </c>
       <c r="Y4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z4">
         <v>6</v>
@@ -850,15 +866,27 @@
         <v>5</v>
       </c>
       <c r="AB4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC4">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:29">
+      <c r="AD4">
+        <v>5</v>
+      </c>
+      <c r="AE4">
+        <v>6</v>
+      </c>
+      <c r="AF4">
+        <v>6</v>
+      </c>
+      <c r="AG4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5">
         <v>9</v>
@@ -882,10 +910,10 @@
         <v>10</v>
       </c>
       <c r="I5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K5">
         <v>10</v>
@@ -894,10 +922,10 @@
         <v>10</v>
       </c>
       <c r="M5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O5">
         <v>10</v>
@@ -924,7 +952,7 @@
         <v>10</v>
       </c>
       <c r="W5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X5">
         <v>10</v>
@@ -936,18 +964,30 @@
         <v>9</v>
       </c>
       <c r="AA5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB5">
         <v>10</v>
       </c>
       <c r="AC5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:29">
+        <v>9</v>
+      </c>
+      <c r="AD5">
+        <v>8</v>
+      </c>
+      <c r="AE5">
+        <v>10</v>
+      </c>
+      <c r="AF5">
+        <v>10</v>
+      </c>
+      <c r="AG5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6">
         <v>6</v>
@@ -974,16 +1014,16 @@
         <v>10</v>
       </c>
       <c r="J6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N6">
         <v>6</v>
@@ -995,48 +1035,60 @@
         <v>6</v>
       </c>
       <c r="Q6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R6">
         <v>6</v>
       </c>
       <c r="S6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T6">
         <v>6</v>
       </c>
       <c r="U6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y6">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB6">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AC6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:29">
+        <v>6</v>
+      </c>
+      <c r="AD6">
+        <v>5</v>
+      </c>
+      <c r="AE6">
+        <v>8</v>
+      </c>
+      <c r="AF6">
+        <v>5</v>
+      </c>
+      <c r="AG6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7">
         <v>9</v>
@@ -1063,19 +1115,19 @@
         <v>10</v>
       </c>
       <c r="J7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L7">
         <v>10</v>
       </c>
       <c r="M7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O7">
         <v>10</v>
@@ -1084,22 +1136,22 @@
         <v>10</v>
       </c>
       <c r="Q7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="S7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U7">
         <v>10</v>
       </c>
       <c r="V7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W7">
         <v>10</v>
@@ -1108,24 +1160,36 @@
         <v>8</v>
       </c>
       <c r="Y7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z7">
         <v>10</v>
       </c>
       <c r="AA7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC7">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:29">
+        <v>10</v>
+      </c>
+      <c r="AD7">
+        <v>7</v>
+      </c>
+      <c r="AE7">
+        <v>10</v>
+      </c>
+      <c r="AF7">
+        <v>9</v>
+      </c>
+      <c r="AG7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8">
         <v>10</v>
@@ -1152,19 +1216,19 @@
         <v>10</v>
       </c>
       <c r="J8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K8">
         <v>9</v>
       </c>
       <c r="L8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O8">
         <v>10</v>
@@ -1173,13 +1237,13 @@
         <v>10</v>
       </c>
       <c r="Q8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R8">
         <v>10</v>
       </c>
       <c r="S8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T8">
         <v>10</v>
@@ -1194,27 +1258,39 @@
         <v>10</v>
       </c>
       <c r="X8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z8">
         <v>10</v>
       </c>
       <c r="AA8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC8">
         <v>10</v>
       </c>
-    </row>
-    <row r="9" spans="1:29">
+      <c r="AD8">
+        <v>10</v>
+      </c>
+      <c r="AE8">
+        <v>10</v>
+      </c>
+      <c r="AF8">
+        <v>10</v>
+      </c>
+      <c r="AG8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9">
         <v>10</v>
@@ -1241,69 +1317,81 @@
         <v>10</v>
       </c>
       <c r="J9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K9">
         <v>9</v>
       </c>
       <c r="L9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M9">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N9">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P9">
         <v>9</v>
       </c>
       <c r="Q9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V9">
         <v>7</v>
       </c>
       <c r="W9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC9">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:29">
+        <v>9</v>
+      </c>
+      <c r="AD9">
+        <v>6</v>
+      </c>
+      <c r="AE9">
+        <v>10</v>
+      </c>
+      <c r="AF9">
+        <v>8</v>
+      </c>
+      <c r="AG9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10">
         <v>8</v>
@@ -1330,7 +1418,7 @@
         <v>10</v>
       </c>
       <c r="J10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K10">
         <v>9</v>
@@ -1339,60 +1427,72 @@
         <v>9</v>
       </c>
       <c r="M10">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N10">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="S10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V10">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC10">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:29">
+        <v>8</v>
+      </c>
+      <c r="AD10">
+        <v>6</v>
+      </c>
+      <c r="AE10">
+        <v>10</v>
+      </c>
+      <c r="AF10">
+        <v>9</v>
+      </c>
+      <c r="AG10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B11">
         <v>8</v>
@@ -1416,46 +1516,46 @@
         <v>6</v>
       </c>
       <c r="I11">
+        <v>10</v>
+      </c>
+      <c r="J11">
         <v>4</v>
       </c>
-      <c r="J11">
-        <v>7</v>
-      </c>
       <c r="K11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P11">
+        <v>6</v>
+      </c>
+      <c r="Q11">
+        <v>10</v>
+      </c>
+      <c r="R11">
         <v>4</v>
       </c>
-      <c r="Q11">
-        <v>5</v>
-      </c>
-      <c r="R11">
+      <c r="S11">
+        <v>5</v>
+      </c>
+      <c r="T11">
         <v>0</v>
       </c>
-      <c r="S11">
-        <v>5</v>
-      </c>
-      <c r="T11">
-        <v>6</v>
-      </c>
       <c r="U11">
         <v>5</v>
       </c>
       <c r="V11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W11">
         <v>5</v>
@@ -1464,7 +1564,7 @@
         <v>5</v>
       </c>
       <c r="Y11">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z11">
         <v>5</v>
@@ -1473,15 +1573,27 @@
         <v>5</v>
       </c>
       <c r="AB11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AC11">
         <v>5</v>
       </c>
-    </row>
-    <row r="12" spans="1:29">
+      <c r="AD11">
+        <v>5</v>
+      </c>
+      <c r="AE11">
+        <v>7</v>
+      </c>
+      <c r="AF11">
+        <v>5</v>
+      </c>
+      <c r="AG11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:33">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12">
         <v>6</v>
@@ -1505,10 +1617,10 @@
         <v>5</v>
       </c>
       <c r="I12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J12">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K12">
         <v>5</v>
@@ -1523,13 +1635,13 @@
         <v>5</v>
       </c>
       <c r="O12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q12">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R12">
         <v>5</v>
@@ -1538,22 +1650,22 @@
         <v>5</v>
       </c>
       <c r="T12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U12">
         <v>5</v>
       </c>
       <c r="V12">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X12">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y12">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z12">
         <v>6</v>
@@ -1567,10 +1679,22 @@
       <c r="AC12">
         <v>6</v>
       </c>
-    </row>
-    <row r="13" spans="1:29">
+      <c r="AD12">
+        <v>5</v>
+      </c>
+      <c r="AE12">
+        <v>5</v>
+      </c>
+      <c r="AF12">
+        <v>6</v>
+      </c>
+      <c r="AG12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13">
         <v>7</v>
@@ -1597,69 +1721,81 @@
         <v>10</v>
       </c>
       <c r="J13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K13">
         <v>9</v>
       </c>
       <c r="L13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R13">
         <v>8</v>
       </c>
       <c r="S13">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W13">
         <v>8</v>
       </c>
       <c r="X13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z13">
         <v>8</v>
       </c>
       <c r="AA13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB13">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC13">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:29">
+        <v>8</v>
+      </c>
+      <c r="AD13">
+        <v>8</v>
+      </c>
+      <c r="AE13">
+        <v>9</v>
+      </c>
+      <c r="AF13">
+        <v>9</v>
+      </c>
+      <c r="AG13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33">
       <c r="A14" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14">
         <v>9</v>
@@ -1686,55 +1822,55 @@
         <v>10</v>
       </c>
       <c r="J14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L14">
         <v>9</v>
       </c>
       <c r="M14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X14">
         <v>7</v>
       </c>
       <c r="Y14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA14">
         <v>7</v>
@@ -1743,12 +1879,24 @@
         <v>9</v>
       </c>
       <c r="AC14">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:29">
+        <v>9</v>
+      </c>
+      <c r="AD14">
+        <v>7</v>
+      </c>
+      <c r="AE14">
+        <v>9</v>
+      </c>
+      <c r="AF14">
+        <v>7</v>
+      </c>
+      <c r="AG14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15">
         <v>9</v>
@@ -1772,7 +1920,7 @@
         <v>10</v>
       </c>
       <c r="I15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J15">
         <v>9</v>
@@ -1784,10 +1932,10 @@
         <v>9</v>
       </c>
       <c r="M15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O15">
         <v>10</v>
@@ -1796,16 +1944,16 @@
         <v>10</v>
       </c>
       <c r="Q15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U15">
         <v>10</v>
@@ -1814,13 +1962,13 @@
         <v>10</v>
       </c>
       <c r="W15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z15">
         <v>9</v>
@@ -1829,15 +1977,27 @@
         <v>9</v>
       </c>
       <c r="AB15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC15">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:29">
+        <v>9</v>
+      </c>
+      <c r="AD15">
+        <v>9</v>
+      </c>
+      <c r="AE15">
+        <v>10</v>
+      </c>
+      <c r="AF15">
+        <v>10</v>
+      </c>
+      <c r="AG15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33">
       <c r="A16" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B16">
         <v>8</v>
@@ -1867,16 +2027,16 @@
         <v>10</v>
       </c>
       <c r="K16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M16">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O16">
         <v>10</v>
@@ -1885,48 +2045,60 @@
         <v>10</v>
       </c>
       <c r="Q16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="S16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T16">
         <v>7</v>
       </c>
       <c r="U16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V16">
         <v>7</v>
       </c>
       <c r="W16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA16">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC16">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:29">
+        <v>8</v>
+      </c>
+      <c r="AD16">
+        <v>6</v>
+      </c>
+      <c r="AE16">
+        <v>10</v>
+      </c>
+      <c r="AF16">
+        <v>9</v>
+      </c>
+      <c r="AG16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:33">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B17">
         <v>9</v>
@@ -1953,69 +2125,81 @@
         <v>10</v>
       </c>
       <c r="J17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="S17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T17">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U17">
         <v>10</v>
       </c>
       <c r="V17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W17">
         <v>10</v>
       </c>
       <c r="X17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z17">
         <v>10</v>
       </c>
       <c r="AA17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC17">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:29">
+        <v>10</v>
+      </c>
+      <c r="AD17">
+        <v>9</v>
+      </c>
+      <c r="AE17">
+        <v>10</v>
+      </c>
+      <c r="AF17">
+        <v>9</v>
+      </c>
+      <c r="AG17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:33">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B18">
         <v>9</v>
@@ -2039,40 +2223,40 @@
         <v>9</v>
       </c>
       <c r="I18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K18">
         <v>9</v>
       </c>
       <c r="L18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M18">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N18">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O18">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="P18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R18">
         <v>8</v>
       </c>
       <c r="S18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U18">
         <v>9</v>
@@ -2081,30 +2265,42 @@
         <v>7</v>
       </c>
       <c r="W18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA18">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC18">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:29">
+        <v>9</v>
+      </c>
+      <c r="AD18">
+        <v>6</v>
+      </c>
+      <c r="AE18">
+        <v>10</v>
+      </c>
+      <c r="AF18">
+        <v>8</v>
+      </c>
+      <c r="AG18">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:33">
       <c r="A19" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B19">
         <v>8</v>
@@ -2131,52 +2327,52 @@
         <v>10</v>
       </c>
       <c r="J19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L19">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M19">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P19">
         <v>8</v>
       </c>
       <c r="Q19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S19">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T19">
         <v>7</v>
       </c>
       <c r="U19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V19">
         <v>7</v>
       </c>
       <c r="W19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z19">
         <v>9</v>
@@ -2185,15 +2381,27 @@
         <v>6</v>
       </c>
       <c r="AB19">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AC19">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:29">
+        <v>9</v>
+      </c>
+      <c r="AD19">
+        <v>6</v>
+      </c>
+      <c r="AE19">
+        <v>9</v>
+      </c>
+      <c r="AF19">
+        <v>7</v>
+      </c>
+      <c r="AG19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:33">
       <c r="A20" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B20">
         <v>7</v>
@@ -2217,31 +2425,31 @@
         <v>7</v>
       </c>
       <c r="I20">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J20">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K20">
         <v>5</v>
       </c>
       <c r="L20">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M20">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N20">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O20">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="P20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q20">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R20">
         <v>6</v>
@@ -2256,16 +2464,16 @@
         <v>5</v>
       </c>
       <c r="V20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W20">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X20">
         <v>5</v>
       </c>
       <c r="Y20">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z20">
         <v>7</v>
@@ -2274,15 +2482,27 @@
         <v>5</v>
       </c>
       <c r="AB20">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AC20">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:29">
+        <v>7</v>
+      </c>
+      <c r="AD20">
+        <v>5</v>
+      </c>
+      <c r="AE20">
+        <v>8</v>
+      </c>
+      <c r="AF20">
+        <v>6</v>
+      </c>
+      <c r="AG20">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:33">
       <c r="A21" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B21">
         <v>7</v>
@@ -2306,55 +2526,55 @@
         <v>7</v>
       </c>
       <c r="I21">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L21">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N21">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="O21">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q21">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S21">
         <v>5</v>
       </c>
       <c r="T21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U21">
         <v>5</v>
       </c>
       <c r="V21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W21">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X21">
         <v>5</v>
       </c>
       <c r="Y21">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z21">
         <v>7</v>
@@ -2363,15 +2583,27 @@
         <v>5</v>
       </c>
       <c r="AB21">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AC21">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:29">
+        <v>7</v>
+      </c>
+      <c r="AD21">
+        <v>5</v>
+      </c>
+      <c r="AE21">
+        <v>7</v>
+      </c>
+      <c r="AF21">
+        <v>6</v>
+      </c>
+      <c r="AG21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:33">
       <c r="A22" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B22">
         <v>9</v>
@@ -2398,69 +2630,81 @@
         <v>10</v>
       </c>
       <c r="J22">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L22">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M22">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N22">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O22">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="P22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q22">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S22">
         <v>6</v>
       </c>
       <c r="T22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U22">
         <v>6</v>
       </c>
       <c r="V22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W22">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="X22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y22">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z22">
         <v>8</v>
       </c>
       <c r="AA22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC22">
         <v>8</v>
       </c>
-    </row>
-    <row r="23" spans="1:29">
+      <c r="AD22">
+        <v>5</v>
+      </c>
+      <c r="AE22">
+        <v>8</v>
+      </c>
+      <c r="AF22">
+        <v>8</v>
+      </c>
+      <c r="AG22">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:33">
       <c r="A23" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B23">
         <v>9</v>
@@ -2487,37 +2731,37 @@
         <v>10</v>
       </c>
       <c r="J23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K23">
         <v>9</v>
       </c>
       <c r="L23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M23">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N23">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O23">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P23">
         <v>8</v>
       </c>
       <c r="Q23">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S23">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U23">
         <v>9</v>
@@ -2532,24 +2776,36 @@
         <v>8</v>
       </c>
       <c r="Y23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z23">
         <v>9</v>
       </c>
       <c r="AA23">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC23">
         <v>9</v>
       </c>
-    </row>
-    <row r="24" spans="1:29">
+      <c r="AD23">
+        <v>6</v>
+      </c>
+      <c r="AE23">
+        <v>10</v>
+      </c>
+      <c r="AF23">
+        <v>9</v>
+      </c>
+      <c r="AG23">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:33">
       <c r="A24" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B24">
         <v>10</v>
@@ -2585,10 +2841,10 @@
         <v>10</v>
       </c>
       <c r="M24">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N24">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O24">
         <v>10</v>
@@ -2618,7 +2874,7 @@
         <v>10</v>
       </c>
       <c r="X24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y24">
         <v>10</v>
@@ -2635,10 +2891,22 @@
       <c r="AC24">
         <v>10</v>
       </c>
-    </row>
-    <row r="25" spans="1:29">
+      <c r="AD24">
+        <v>9</v>
+      </c>
+      <c r="AE24">
+        <v>10</v>
+      </c>
+      <c r="AF24">
+        <v>10</v>
+      </c>
+      <c r="AG24">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:33">
       <c r="A25" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B25">
         <v>5</v>
@@ -2662,17 +2930,17 @@
         <v>5</v>
       </c>
       <c r="I25">
+        <v>10</v>
+      </c>
+      <c r="J25">
         <v>4</v>
       </c>
-      <c r="J25">
-        <v>5</v>
-      </c>
       <c r="K25">
+        <v>5</v>
+      </c>
+      <c r="L25">
         <v>0</v>
       </c>
-      <c r="L25">
-        <v>5</v>
-      </c>
       <c r="M25">
         <v>5</v>
       </c>
@@ -2683,34 +2951,34 @@
         <v>5</v>
       </c>
       <c r="P25">
+        <v>5</v>
+      </c>
+      <c r="Q25">
+        <v>10</v>
+      </c>
+      <c r="R25">
         <v>3</v>
       </c>
-      <c r="Q25">
-        <v>5</v>
-      </c>
-      <c r="R25">
+      <c r="S25">
+        <v>5</v>
+      </c>
+      <c r="T25">
         <v>0</v>
       </c>
-      <c r="S25">
-        <v>5</v>
-      </c>
-      <c r="T25">
-        <v>5</v>
-      </c>
       <c r="U25">
         <v>5</v>
       </c>
       <c r="V25">
+        <v>5</v>
+      </c>
+      <c r="W25">
+        <v>5</v>
+      </c>
+      <c r="X25">
         <v>0</v>
       </c>
-      <c r="W25">
-        <v>5</v>
-      </c>
-      <c r="X25">
-        <v>5</v>
-      </c>
       <c r="Y25">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z25">
         <v>5</v>
@@ -2724,10 +2992,22 @@
       <c r="AC25">
         <v>5</v>
       </c>
-    </row>
-    <row r="26" spans="1:29">
+      <c r="AD25">
+        <v>5</v>
+      </c>
+      <c r="AE25">
+        <v>5</v>
+      </c>
+      <c r="AF25">
+        <v>5</v>
+      </c>
+      <c r="AG25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:33">
       <c r="A26" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B26">
         <v>10</v>
@@ -2754,19 +3034,19 @@
         <v>10</v>
       </c>
       <c r="J26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K26">
         <v>9</v>
       </c>
       <c r="L26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M26">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N26">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O26">
         <v>10</v>
@@ -2775,48 +3055,60 @@
         <v>10</v>
       </c>
       <c r="Q26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S26">
         <v>9</v>
       </c>
       <c r="T26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W26">
         <v>10</v>
       </c>
       <c r="X26">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA26">
         <v>8</v>
       </c>
       <c r="AB26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC26">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="27" spans="1:29">
+        <v>9</v>
+      </c>
+      <c r="AD26">
+        <v>8</v>
+      </c>
+      <c r="AE26">
+        <v>10</v>
+      </c>
+      <c r="AF26">
+        <v>10</v>
+      </c>
+      <c r="AG26">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:33">
       <c r="A27" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B27">
         <v>9</v>
@@ -2843,69 +3135,81 @@
         <v>10</v>
       </c>
       <c r="J27">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K27">
         <v>8</v>
       </c>
       <c r="L27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N27">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q27">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R27">
         <v>10</v>
       </c>
       <c r="S27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T27">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U27">
         <v>10</v>
       </c>
       <c r="V27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W27">
         <v>10</v>
       </c>
       <c r="X27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y27">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z27">
         <v>10</v>
       </c>
       <c r="AA27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC27">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="28" spans="1:29">
+        <v>10</v>
+      </c>
+      <c r="AD27">
+        <v>7</v>
+      </c>
+      <c r="AE27">
+        <v>10</v>
+      </c>
+      <c r="AF27">
+        <v>9</v>
+      </c>
+      <c r="AG27">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:33">
       <c r="A28" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B28">
         <v>8</v>
@@ -2929,43 +3233,43 @@
         <v>8</v>
       </c>
       <c r="I28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J28">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K28">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L28">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N28">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P28">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q28">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R28">
         <v>7</v>
       </c>
       <c r="S28">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V28">
         <v>8</v>
@@ -2974,10 +3278,10 @@
         <v>8</v>
       </c>
       <c r="X28">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y28">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z28">
         <v>8</v>
@@ -2986,15 +3290,27 @@
         <v>6</v>
       </c>
       <c r="AB28">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC28">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="29" spans="1:29">
+        <v>8</v>
+      </c>
+      <c r="AD28">
+        <v>6</v>
+      </c>
+      <c r="AE28">
+        <v>9</v>
+      </c>
+      <c r="AF28">
+        <v>9</v>
+      </c>
+      <c r="AG28">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:33">
       <c r="A29" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B29">
         <v>9</v>
@@ -3018,37 +3334,37 @@
         <v>9</v>
       </c>
       <c r="I29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J29">
         <v>9</v>
       </c>
       <c r="K29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M29">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N29">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R29">
         <v>9</v>
       </c>
       <c r="S29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T29">
         <v>9</v>
@@ -3057,33 +3373,45 @@
         <v>10</v>
       </c>
       <c r="V29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X29">
         <v>8</v>
       </c>
       <c r="Y29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA29">
         <v>8</v>
       </c>
       <c r="AB29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC29">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="30" spans="1:29">
+        <v>10</v>
+      </c>
+      <c r="AD29">
+        <v>8</v>
+      </c>
+      <c r="AE29">
+        <v>10</v>
+      </c>
+      <c r="AF29">
+        <v>8</v>
+      </c>
+      <c r="AG29">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:33">
       <c r="A30" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B30">
         <v>8</v>
@@ -3110,7 +3438,7 @@
         <v>10</v>
       </c>
       <c r="J30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K30">
         <v>8</v>
@@ -3119,28 +3447,28 @@
         <v>8</v>
       </c>
       <c r="M30">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N30">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="S30">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U30">
         <v>9</v>
@@ -3155,24 +3483,36 @@
         <v>7</v>
       </c>
       <c r="Y30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB30">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC30">
         <v>8</v>
       </c>
-    </row>
-    <row r="31" spans="1:29">
+      <c r="AD30">
+        <v>6</v>
+      </c>
+      <c r="AE30">
+        <v>10</v>
+      </c>
+      <c r="AF30">
+        <v>8</v>
+      </c>
+      <c r="AG30">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="1:33">
       <c r="A31" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B31">
         <v>9</v>
@@ -3199,19 +3539,19 @@
         <v>10</v>
       </c>
       <c r="J31">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K31">
         <v>8</v>
       </c>
       <c r="L31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M31">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N31">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O31">
         <v>9</v>
@@ -3220,48 +3560,60 @@
         <v>9</v>
       </c>
       <c r="Q31">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R31">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="S31">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T31">
         <v>7</v>
       </c>
       <c r="U31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V31">
         <v>7</v>
       </c>
       <c r="W31">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X31">
         <v>7</v>
       </c>
       <c r="Y31">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z31">
         <v>9</v>
       </c>
       <c r="AA31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC31">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="32" spans="1:29">
+        <v>9</v>
+      </c>
+      <c r="AD31">
+        <v>6</v>
+      </c>
+      <c r="AE31">
+        <v>9</v>
+      </c>
+      <c r="AF31">
+        <v>8</v>
+      </c>
+      <c r="AG31">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:33">
       <c r="A32" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B32">
         <v>7</v>
@@ -3285,72 +3637,84 @@
         <v>8</v>
       </c>
       <c r="I32">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K32">
         <v>7</v>
       </c>
       <c r="L32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M32">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N32">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="O32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P32">
         <v>8</v>
       </c>
       <c r="Q32">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W32">
         <v>8</v>
       </c>
       <c r="X32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y32">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z32">
         <v>8</v>
       </c>
       <c r="AA32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB32">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AC32">
         <v>8</v>
       </c>
-    </row>
-    <row r="33" spans="1:29">
+      <c r="AD32">
+        <v>5</v>
+      </c>
+      <c r="AE32">
+        <v>9</v>
+      </c>
+      <c r="AF32">
+        <v>8</v>
+      </c>
+      <c r="AG32">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:33">
       <c r="A33" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B33">
         <v>9</v>
@@ -3377,69 +3741,81 @@
         <v>10</v>
       </c>
       <c r="J33">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K33">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L33">
         <v>8</v>
       </c>
       <c r="M33">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N33">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O33">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P33">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Q33">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R33">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U33">
         <v>5</v>
       </c>
       <c r="V33">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W33">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="X33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y33">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA33">
         <v>6</v>
       </c>
       <c r="AB33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC33">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:29">
+        <v>8</v>
+      </c>
+      <c r="AD33">
+        <v>6</v>
+      </c>
+      <c r="AE33">
+        <v>8</v>
+      </c>
+      <c r="AF33">
+        <v>6</v>
+      </c>
+      <c r="AG33">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" spans="1:33">
       <c r="A34" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B34">
         <v>9</v>
@@ -3466,69 +3842,81 @@
         <v>10</v>
       </c>
       <c r="J34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K34">
         <v>9</v>
       </c>
       <c r="L34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M34">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N34">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P34">
         <v>9</v>
       </c>
       <c r="Q34">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R34">
         <v>9</v>
       </c>
       <c r="S34">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V34">
         <v>8</v>
       </c>
       <c r="W34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X34">
         <v>8</v>
       </c>
       <c r="Y34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z34">
         <v>9</v>
       </c>
       <c r="AA34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC34">
         <v>9</v>
       </c>
-    </row>
-    <row r="35" spans="1:29">
+      <c r="AD34">
+        <v>7</v>
+      </c>
+      <c r="AE34">
+        <v>10</v>
+      </c>
+      <c r="AF34">
+        <v>9</v>
+      </c>
+      <c r="AG34">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="1:33">
       <c r="A35" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B35">
         <v>7</v>
@@ -3555,7 +3943,7 @@
         <v>10</v>
       </c>
       <c r="J35">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K35">
         <v>8</v>
@@ -3564,25 +3952,25 @@
         <v>8</v>
       </c>
       <c r="M35">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N35">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O35">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P35">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q35">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R35">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="S35">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T35">
         <v>8</v>
@@ -3597,27 +3985,39 @@
         <v>9</v>
       </c>
       <c r="X35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y35">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB35">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC35">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="36" spans="1:29">
+        <v>8</v>
+      </c>
+      <c r="AD35">
+        <v>6</v>
+      </c>
+      <c r="AE35">
+        <v>9</v>
+      </c>
+      <c r="AF35">
+        <v>7</v>
+      </c>
+      <c r="AG35">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:33">
       <c r="A36" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B36">
         <v>8</v>
@@ -3644,37 +4044,37 @@
         <v>10</v>
       </c>
       <c r="J36">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K36">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L36">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M36">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N36">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O36">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P36">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q36">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R36">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="S36">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T36">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U36">
         <v>10</v>
@@ -3683,13 +4083,13 @@
         <v>7</v>
       </c>
       <c r="W36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y36">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z36">
         <v>9</v>
@@ -3698,15 +4098,27 @@
         <v>6</v>
       </c>
       <c r="AB36">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC36">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="37" spans="1:29">
+        <v>9</v>
+      </c>
+      <c r="AD36">
+        <v>6</v>
+      </c>
+      <c r="AE36">
+        <v>10</v>
+      </c>
+      <c r="AF36">
+        <v>8</v>
+      </c>
+      <c r="AG36">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="1:33">
       <c r="A37" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B37">
         <v>8</v>
@@ -3733,69 +4145,81 @@
         <v>10</v>
       </c>
       <c r="J37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K37">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L37">
         <v>7</v>
       </c>
       <c r="M37">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N37">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O37">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P37">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q37">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S37">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T37">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U37">
         <v>10</v>
       </c>
       <c r="V37">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y37">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z37">
         <v>9</v>
       </c>
       <c r="AA37">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB37">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC37">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="38" spans="1:29">
+        <v>9</v>
+      </c>
+      <c r="AD37">
+        <v>6</v>
+      </c>
+      <c r="AE37">
+        <v>10</v>
+      </c>
+      <c r="AF37">
+        <v>7</v>
+      </c>
+      <c r="AG37">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" spans="1:33">
       <c r="A38" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B38">
         <v>8</v>
@@ -3819,55 +4243,55 @@
         <v>9</v>
       </c>
       <c r="I38">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J38">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K38">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L38">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M38">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O38">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="P38">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q38">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R38">
         <v>10</v>
       </c>
       <c r="S38">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T38">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U38">
         <v>10</v>
       </c>
       <c r="V38">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W38">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X38">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Y38">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z38">
         <v>9</v>
@@ -3876,15 +4300,27 @@
         <v>6</v>
       </c>
       <c r="AB38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC38">
         <v>9</v>
       </c>
-    </row>
-    <row r="39" spans="1:29">
+      <c r="AD38">
+        <v>6</v>
+      </c>
+      <c r="AE38">
+        <v>8</v>
+      </c>
+      <c r="AF38">
+        <v>9</v>
+      </c>
+      <c r="AG38">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" spans="1:33">
       <c r="A39" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B39">
         <v>7</v>
@@ -3908,34 +4344,34 @@
         <v>8</v>
       </c>
       <c r="I39">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J39">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K39">
         <v>6</v>
       </c>
       <c r="L39">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M39">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N39">
         <v>6</v>
       </c>
       <c r="O39">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P39">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q39">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R39">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S39">
         <v>8</v>
@@ -3944,19 +4380,19 @@
         <v>7</v>
       </c>
       <c r="U39">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V39">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W39">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X39">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y39">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z39">
         <v>8</v>
@@ -3965,15 +4401,27 @@
         <v>6</v>
       </c>
       <c r="AB39">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AC39">
         <v>8</v>
       </c>
-    </row>
-    <row r="40" spans="1:29">
+      <c r="AD39">
+        <v>6</v>
+      </c>
+      <c r="AE39">
+        <v>8</v>
+      </c>
+      <c r="AF39">
+        <v>8</v>
+      </c>
+      <c r="AG39">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="1:33">
       <c r="A40" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B40">
         <v>9</v>
@@ -4000,69 +4448,81 @@
         <v>10</v>
       </c>
       <c r="J40">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K40">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L40">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M40">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N40">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O40">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P40">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q40">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R40">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S40">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T40">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U40">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V40">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W40">
         <v>10</v>
       </c>
       <c r="X40">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y40">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z40">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA40">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB40">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC40">
         <v>9</v>
       </c>
-    </row>
-    <row r="41" spans="1:29">
+      <c r="AD40">
+        <v>6</v>
+      </c>
+      <c r="AE40">
+        <v>10</v>
+      </c>
+      <c r="AF40">
+        <v>9</v>
+      </c>
+      <c r="AG40">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41" spans="1:33">
       <c r="A41" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B41">
         <v>9</v>
@@ -4092,16 +4552,16 @@
         <v>10</v>
       </c>
       <c r="K41">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L41">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M41">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N41">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O41">
         <v>10</v>
@@ -4125,7 +4585,7 @@
         <v>10</v>
       </c>
       <c r="V41">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W41">
         <v>10</v>
@@ -4134,24 +4594,36 @@
         <v>9</v>
       </c>
       <c r="Y41">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z41">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA41">
         <v>9</v>
       </c>
       <c r="AB41">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC41">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="42" spans="1:29">
+        <v>9</v>
+      </c>
+      <c r="AD41">
+        <v>9</v>
+      </c>
+      <c r="AE41">
+        <v>10</v>
+      </c>
+      <c r="AF41">
+        <v>10</v>
+      </c>
+      <c r="AG41">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="1:33">
       <c r="A42" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B42">
         <v>8</v>
@@ -4178,72 +4650,84 @@
         <v>10</v>
       </c>
       <c r="J42">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K42">
         <v>8</v>
       </c>
       <c r="L42">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N42">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O42">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P42">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q42">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R42">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="S42">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T42">
         <v>7</v>
       </c>
       <c r="U42">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V42">
         <v>7</v>
       </c>
       <c r="W42">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X42">
         <v>7</v>
       </c>
       <c r="Y42">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z42">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB42">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC42">
         <v>7</v>
+      </c>
+      <c r="AD42">
+        <v>6</v>
+      </c>
+      <c r="AE42">
+        <v>10</v>
+      </c>
+      <c r="AF42">
+        <v>7</v>
+      </c>
+      <c r="AG42">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="I1:O1"/>
-    <mergeCell ref="P1:V1"/>
-    <mergeCell ref="W1:AC1"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="J1:Q1"/>
+    <mergeCell ref="R1:Y1"/>
+    <mergeCell ref="Z1:AG1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4251,16 +4735,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V42"/>
+  <dimension ref="A1:Y42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:25">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -4268,26 +4752,29 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="J1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1" t="s">
+        <v>54</v>
+      </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
-      <c r="P1" s="1" t="s">
-        <v>54</v>
-      </c>
+      <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
+      <c r="R1" s="1" t="s">
+        <v>55</v>
+      </c>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
-    </row>
-    <row r="2" spans="1:22">
+      <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
+    </row>
+    <row r="2" spans="1:25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -4313,56 +4800,65 @@
         <v>11</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="Q2" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="X2" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:22">
+      <c r="Y2" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25">
       <c r="A3" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4">
         <v>80</v>
@@ -4386,51 +4882,60 @@
         <v>100</v>
       </c>
       <c r="I4">
+        <v>100</v>
+      </c>
+      <c r="J4">
         <v>90</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>83.3</v>
       </c>
-      <c r="K4">
-        <v>100</v>
-      </c>
       <c r="L4">
         <v>100</v>
       </c>
       <c r="M4">
+        <v>100</v>
+      </c>
+      <c r="N4">
         <v>80</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>87.5</v>
       </c>
-      <c r="O4">
-        <v>100</v>
-      </c>
       <c r="P4">
+        <v>100</v>
+      </c>
+      <c r="Q4">
+        <v>100</v>
+      </c>
+      <c r="R4">
         <v>93.3</v>
       </c>
-      <c r="Q4">
+      <c r="S4">
         <v>83.3</v>
       </c>
-      <c r="R4">
-        <v>100</v>
-      </c>
-      <c r="S4">
-        <v>100</v>
-      </c>
       <c r="T4">
+        <v>100</v>
+      </c>
+      <c r="U4">
+        <v>100</v>
+      </c>
+      <c r="V4">
         <v>85</v>
       </c>
-      <c r="U4">
+      <c r="W4">
         <v>85.40000000000001</v>
       </c>
-      <c r="V4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22">
+      <c r="X4">
+        <v>100</v>
+      </c>
+      <c r="Y4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5">
         <v>100</v>
@@ -4454,17 +4959,17 @@
         <v>95</v>
       </c>
       <c r="I5">
+        <v>100</v>
+      </c>
+      <c r="J5">
         <v>95</v>
       </c>
-      <c r="J5">
-        <v>100</v>
-      </c>
       <c r="K5">
+        <v>100</v>
+      </c>
+      <c r="L5">
         <v>97.5</v>
       </c>
-      <c r="L5">
-        <v>100</v>
-      </c>
       <c r="M5">
         <v>100</v>
       </c>
@@ -4472,33 +4977,42 @@
         <v>100</v>
       </c>
       <c r="O5">
+        <v>100</v>
+      </c>
+      <c r="P5">
         <v>92.5</v>
       </c>
-      <c r="P5">
+      <c r="Q5">
+        <v>100</v>
+      </c>
+      <c r="R5">
         <v>90</v>
       </c>
-      <c r="Q5">
-        <v>100</v>
-      </c>
-      <c r="R5">
+      <c r="S5">
+        <v>100</v>
+      </c>
+      <c r="T5">
         <v>98.40000000000001</v>
       </c>
-      <c r="S5">
-        <v>100</v>
-      </c>
-      <c r="T5">
-        <v>100</v>
-      </c>
       <c r="U5">
         <v>100</v>
       </c>
       <c r="V5">
+        <v>100</v>
+      </c>
+      <c r="W5">
+        <v>100</v>
+      </c>
+      <c r="X5">
         <v>95.3</v>
       </c>
-    </row>
-    <row r="6" spans="1:22">
+      <c r="Y5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6">
         <v>80</v>
@@ -4522,51 +5036,60 @@
         <v>100</v>
       </c>
       <c r="I6">
+        <v>100</v>
+      </c>
+      <c r="J6">
         <v>90</v>
       </c>
-      <c r="J6">
+      <c r="K6">
         <v>93.3</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>97.5</v>
       </c>
-      <c r="L6">
-        <v>100</v>
-      </c>
       <c r="M6">
+        <v>100</v>
+      </c>
+      <c r="N6">
         <v>95</v>
       </c>
-      <c r="N6">
-        <v>100</v>
-      </c>
       <c r="O6">
+        <v>100</v>
+      </c>
+      <c r="P6">
         <v>95</v>
       </c>
-      <c r="P6">
+      <c r="Q6">
+        <v>100</v>
+      </c>
+      <c r="R6">
         <v>93.3</v>
       </c>
-      <c r="Q6">
+      <c r="S6">
         <v>95.8</v>
       </c>
-      <c r="R6">
+      <c r="T6">
         <v>98.40000000000001</v>
       </c>
-      <c r="S6">
-        <v>100</v>
-      </c>
-      <c r="T6">
+      <c r="U6">
+        <v>100</v>
+      </c>
+      <c r="V6">
         <v>93.3</v>
       </c>
-      <c r="U6">
+      <c r="W6">
         <v>97.90000000000001</v>
       </c>
-      <c r="V6">
+      <c r="X6">
         <v>93.8</v>
       </c>
-    </row>
-    <row r="7" spans="1:22">
+      <c r="Y6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7">
         <v>100</v>
@@ -4596,14 +5119,14 @@
         <v>100</v>
       </c>
       <c r="K7">
+        <v>100</v>
+      </c>
+      <c r="L7">
         <v>92.5</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>90</v>
       </c>
-      <c r="M7">
-        <v>100</v>
-      </c>
       <c r="N7">
         <v>100</v>
       </c>
@@ -4617,24 +5140,33 @@
         <v>100</v>
       </c>
       <c r="R7">
+        <v>100</v>
+      </c>
+      <c r="S7">
+        <v>100</v>
+      </c>
+      <c r="T7">
         <v>93.8</v>
       </c>
-      <c r="S7">
+      <c r="U7">
         <v>93.8</v>
       </c>
-      <c r="T7">
-        <v>100</v>
-      </c>
-      <c r="U7">
-        <v>100</v>
-      </c>
       <c r="V7">
         <v>100</v>
       </c>
-    </row>
-    <row r="8" spans="1:22">
+      <c r="W7">
+        <v>100</v>
+      </c>
+      <c r="X7">
+        <v>100</v>
+      </c>
+      <c r="Y7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8">
         <v>100</v>
@@ -4664,20 +5196,20 @@
         <v>100</v>
       </c>
       <c r="K8">
+        <v>100</v>
+      </c>
+      <c r="L8">
         <v>95</v>
       </c>
-      <c r="L8">
-        <v>100</v>
-      </c>
       <c r="M8">
         <v>100</v>
       </c>
       <c r="N8">
+        <v>100</v>
+      </c>
+      <c r="O8">
         <v>96.90000000000001</v>
       </c>
-      <c r="O8">
-        <v>100</v>
-      </c>
       <c r="P8">
         <v>100</v>
       </c>
@@ -4685,24 +5217,33 @@
         <v>100</v>
       </c>
       <c r="R8">
+        <v>100</v>
+      </c>
+      <c r="S8">
+        <v>100</v>
+      </c>
+      <c r="T8">
         <v>96.90000000000001</v>
       </c>
-      <c r="S8">
-        <v>100</v>
-      </c>
-      <c r="T8">
+      <c r="U8">
+        <v>100</v>
+      </c>
+      <c r="V8">
         <v>93.3</v>
       </c>
-      <c r="U8">
+      <c r="W8">
         <v>97.90000000000001</v>
       </c>
-      <c r="V8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22">
+      <c r="X8">
+        <v>100</v>
+      </c>
+      <c r="Y8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9">
         <v>100</v>
@@ -4729,14 +5270,14 @@
         <v>100</v>
       </c>
       <c r="J9">
+        <v>100</v>
+      </c>
+      <c r="K9">
         <v>93.3</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>97.5</v>
       </c>
-      <c r="L9">
-        <v>100</v>
-      </c>
       <c r="M9">
         <v>100</v>
       </c>
@@ -4744,33 +5285,42 @@
         <v>100</v>
       </c>
       <c r="O9">
+        <v>100</v>
+      </c>
+      <c r="P9">
         <v>97.5</v>
       </c>
-      <c r="P9">
+      <c r="Q9">
+        <v>100</v>
+      </c>
+      <c r="R9">
         <v>96.7</v>
       </c>
-      <c r="Q9">
+      <c r="S9">
         <v>95.8</v>
       </c>
-      <c r="R9">
+      <c r="T9">
         <v>98.40000000000001</v>
       </c>
-      <c r="S9">
-        <v>100</v>
-      </c>
-      <c r="T9">
-        <v>100</v>
-      </c>
       <c r="U9">
+        <v>100</v>
+      </c>
+      <c r="V9">
+        <v>100</v>
+      </c>
+      <c r="W9">
         <v>97.90000000000001</v>
       </c>
-      <c r="V9">
+      <c r="X9">
         <v>98.40000000000001</v>
       </c>
-    </row>
-    <row r="10" spans="1:22">
+      <c r="Y9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10">
         <v>100</v>
@@ -4803,11 +5353,11 @@
         <v>100</v>
       </c>
       <c r="L10">
+        <v>100</v>
+      </c>
+      <c r="M10">
         <v>93.3</v>
       </c>
-      <c r="M10">
-        <v>100</v>
-      </c>
       <c r="N10">
         <v>100</v>
       </c>
@@ -4824,21 +5374,30 @@
         <v>100</v>
       </c>
       <c r="S10">
+        <v>100</v>
+      </c>
+      <c r="T10">
+        <v>100</v>
+      </c>
+      <c r="U10">
         <v>95.8</v>
       </c>
-      <c r="T10">
-        <v>100</v>
-      </c>
-      <c r="U10">
-        <v>100</v>
-      </c>
       <c r="V10">
         <v>100</v>
       </c>
-    </row>
-    <row r="11" spans="1:22">
+      <c r="W10">
+        <v>100</v>
+      </c>
+      <c r="X10">
+        <v>100</v>
+      </c>
+      <c r="Y10">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B11">
         <v>100</v>
@@ -4862,17 +5421,17 @@
         <v>100</v>
       </c>
       <c r="I11">
+        <v>100</v>
+      </c>
+      <c r="J11">
         <v>70</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>90</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>92.5</v>
       </c>
-      <c r="L11">
-        <v>100</v>
-      </c>
       <c r="M11">
         <v>100</v>
       </c>
@@ -4880,33 +5439,42 @@
         <v>100</v>
       </c>
       <c r="O11">
+        <v>100</v>
+      </c>
+      <c r="P11">
         <v>90</v>
       </c>
-      <c r="P11">
+      <c r="Q11">
+        <v>100</v>
+      </c>
+      <c r="R11">
         <v>46.7</v>
       </c>
-      <c r="Q11">
+      <c r="S11">
         <v>56.3</v>
       </c>
-      <c r="R11">
+      <c r="T11">
         <v>57.8</v>
       </c>
-      <c r="S11">
+      <c r="U11">
         <v>62.5</v>
       </c>
-      <c r="T11">
+      <c r="V11">
         <v>66.7</v>
       </c>
-      <c r="U11">
+      <c r="W11">
         <v>93.8</v>
       </c>
-      <c r="V11">
+      <c r="X11">
         <v>56.3</v>
       </c>
-    </row>
-    <row r="12" spans="1:22">
+      <c r="Y11">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12">
         <v>80</v>
@@ -4930,51 +5498,60 @@
         <v>90</v>
       </c>
       <c r="I12">
+        <v>100</v>
+      </c>
+      <c r="J12">
         <v>80</v>
       </c>
-      <c r="J12">
-        <v>100</v>
-      </c>
       <c r="K12">
+        <v>100</v>
+      </c>
+      <c r="L12">
         <v>85</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>86.7</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <v>90</v>
       </c>
-      <c r="N12">
+      <c r="O12">
         <v>84.40000000000001</v>
       </c>
-      <c r="O12">
+      <c r="P12">
         <v>85</v>
       </c>
-      <c r="P12">
+      <c r="Q12">
+        <v>100</v>
+      </c>
+      <c r="R12">
         <v>80</v>
       </c>
-      <c r="Q12">
-        <v>100</v>
-      </c>
-      <c r="R12">
+      <c r="S12">
+        <v>100</v>
+      </c>
+      <c r="T12">
         <v>84.40000000000001</v>
       </c>
-      <c r="S12">
+      <c r="U12">
         <v>85.40000000000001</v>
       </c>
-      <c r="T12">
+      <c r="V12">
         <v>93.3</v>
       </c>
-      <c r="U12">
+      <c r="W12">
         <v>60.4</v>
       </c>
-      <c r="V12">
+      <c r="X12">
         <v>90.59999999999999</v>
       </c>
-    </row>
-    <row r="13" spans="1:22">
+      <c r="Y12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13">
         <v>80</v>
@@ -4998,20 +5575,20 @@
         <v>100</v>
       </c>
       <c r="I13">
+        <v>100</v>
+      </c>
+      <c r="J13">
         <v>90</v>
       </c>
-      <c r="J13">
-        <v>100</v>
-      </c>
       <c r="K13">
         <v>100</v>
       </c>
       <c r="L13">
+        <v>100</v>
+      </c>
+      <c r="M13">
         <v>93.3</v>
       </c>
-      <c r="M13">
-        <v>100</v>
-      </c>
       <c r="N13">
         <v>100</v>
       </c>
@@ -5019,30 +5596,39 @@
         <v>100</v>
       </c>
       <c r="P13">
+        <v>100</v>
+      </c>
+      <c r="Q13">
+        <v>100</v>
+      </c>
+      <c r="R13">
         <v>93.3</v>
       </c>
-      <c r="Q13">
-        <v>100</v>
-      </c>
-      <c r="R13">
-        <v>100</v>
-      </c>
       <c r="S13">
+        <v>100</v>
+      </c>
+      <c r="T13">
+        <v>100</v>
+      </c>
+      <c r="U13">
         <v>95.8</v>
       </c>
-      <c r="T13">
-        <v>100</v>
-      </c>
-      <c r="U13">
+      <c r="V13">
+        <v>100</v>
+      </c>
+      <c r="W13">
         <v>93.8</v>
       </c>
-      <c r="V13">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22">
+      <c r="X13">
+        <v>100</v>
+      </c>
+      <c r="Y13">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25">
       <c r="A14" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14">
         <v>100</v>
@@ -5072,45 +5658,54 @@
         <v>100</v>
       </c>
       <c r="K14">
+        <v>100</v>
+      </c>
+      <c r="L14">
         <v>97.5</v>
       </c>
-      <c r="L14">
+      <c r="M14">
         <v>86.7</v>
       </c>
-      <c r="M14">
-        <v>100</v>
-      </c>
       <c r="N14">
+        <v>100</v>
+      </c>
+      <c r="O14">
         <v>93.8</v>
       </c>
-      <c r="O14">
+      <c r="P14">
         <v>95</v>
       </c>
-      <c r="P14">
-        <v>100</v>
-      </c>
       <c r="Q14">
         <v>100</v>
       </c>
       <c r="R14">
+        <v>100</v>
+      </c>
+      <c r="S14">
+        <v>100</v>
+      </c>
+      <c r="T14">
         <v>96.90000000000001</v>
-      </c>
-      <c r="S14">
-        <v>91.7</v>
-      </c>
-      <c r="T14">
-        <v>100</v>
       </c>
       <c r="U14">
         <v>91.7</v>
       </c>
       <c r="V14">
+        <v>100</v>
+      </c>
+      <c r="W14">
+        <v>91.7</v>
+      </c>
+      <c r="X14">
         <v>96.90000000000001</v>
       </c>
-    </row>
-    <row r="15" spans="1:22">
+      <c r="Y14">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15">
         <v>100</v>
@@ -5134,17 +5729,17 @@
         <v>100</v>
       </c>
       <c r="I15">
+        <v>100</v>
+      </c>
+      <c r="J15">
         <v>95</v>
       </c>
-      <c r="J15">
-        <v>100</v>
-      </c>
       <c r="K15">
+        <v>100</v>
+      </c>
+      <c r="L15">
         <v>97.5</v>
       </c>
-      <c r="L15">
-        <v>100</v>
-      </c>
       <c r="M15">
         <v>100</v>
       </c>
@@ -5155,30 +5750,39 @@
         <v>100</v>
       </c>
       <c r="P15">
+        <v>100</v>
+      </c>
+      <c r="Q15">
+        <v>100</v>
+      </c>
+      <c r="R15">
         <v>96.7</v>
       </c>
-      <c r="Q15">
-        <v>100</v>
-      </c>
-      <c r="R15">
+      <c r="S15">
+        <v>100</v>
+      </c>
+      <c r="T15">
         <v>96.90000000000001</v>
       </c>
-      <c r="S15">
-        <v>100</v>
-      </c>
-      <c r="T15">
-        <v>100</v>
-      </c>
       <c r="U15">
         <v>100</v>
       </c>
       <c r="V15">
         <v>100</v>
       </c>
-    </row>
-    <row r="16" spans="1:22">
+      <c r="W15">
+        <v>100</v>
+      </c>
+      <c r="X15">
+        <v>100</v>
+      </c>
+      <c r="Y15">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25">
       <c r="A16" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B16">
         <v>100</v>
@@ -5229,24 +5833,33 @@
         <v>100</v>
       </c>
       <c r="R16">
+        <v>100</v>
+      </c>
+      <c r="S16">
+        <v>100</v>
+      </c>
+      <c r="T16">
         <v>98.40000000000001</v>
       </c>
-      <c r="S16">
-        <v>100</v>
-      </c>
-      <c r="T16">
-        <v>100</v>
-      </c>
       <c r="U16">
         <v>100</v>
       </c>
       <c r="V16">
         <v>100</v>
       </c>
-    </row>
-    <row r="17" spans="1:22">
+      <c r="W16">
+        <v>100</v>
+      </c>
+      <c r="X16">
+        <v>100</v>
+      </c>
+      <c r="Y16">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B17">
         <v>100</v>
@@ -5276,11 +5889,11 @@
         <v>100</v>
       </c>
       <c r="K17">
+        <v>100</v>
+      </c>
+      <c r="L17">
         <v>97.5</v>
       </c>
-      <c r="L17">
-        <v>100</v>
-      </c>
       <c r="M17">
         <v>100</v>
       </c>
@@ -5297,24 +5910,33 @@
         <v>100</v>
       </c>
       <c r="R17">
+        <v>100</v>
+      </c>
+      <c r="S17">
+        <v>100</v>
+      </c>
+      <c r="T17">
         <v>98.40000000000001</v>
       </c>
-      <c r="S17">
-        <v>100</v>
-      </c>
-      <c r="T17">
-        <v>100</v>
-      </c>
       <c r="U17">
         <v>100</v>
       </c>
       <c r="V17">
         <v>100</v>
       </c>
-    </row>
-    <row r="18" spans="1:22">
+      <c r="W17">
+        <v>100</v>
+      </c>
+      <c r="X17">
+        <v>100</v>
+      </c>
+      <c r="Y17">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B18">
         <v>100</v>
@@ -5338,17 +5960,17 @@
         <v>100</v>
       </c>
       <c r="I18">
+        <v>100</v>
+      </c>
+      <c r="J18">
         <v>90</v>
       </c>
-      <c r="J18">
-        <v>100</v>
-      </c>
       <c r="K18">
+        <v>100</v>
+      </c>
+      <c r="L18">
         <v>97.5</v>
       </c>
-      <c r="L18">
-        <v>100</v>
-      </c>
       <c r="M18">
         <v>100</v>
       </c>
@@ -5359,30 +5981,39 @@
         <v>100</v>
       </c>
       <c r="P18">
+        <v>100</v>
+      </c>
+      <c r="Q18">
+        <v>100</v>
+      </c>
+      <c r="R18">
         <v>93.3</v>
       </c>
-      <c r="Q18">
-        <v>100</v>
-      </c>
-      <c r="R18">
+      <c r="S18">
+        <v>100</v>
+      </c>
+      <c r="T18">
         <v>98.40000000000001</v>
       </c>
-      <c r="S18">
-        <v>100</v>
-      </c>
-      <c r="T18">
-        <v>100</v>
-      </c>
       <c r="U18">
+        <v>100</v>
+      </c>
+      <c r="V18">
+        <v>100</v>
+      </c>
+      <c r="W18">
         <v>97.90000000000001</v>
       </c>
-      <c r="V18">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22">
+      <c r="X18">
+        <v>100</v>
+      </c>
+      <c r="Y18">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25">
       <c r="A19" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B19">
         <v>100</v>
@@ -5409,48 +6040,57 @@
         <v>100</v>
       </c>
       <c r="J19">
+        <v>100</v>
+      </c>
+      <c r="K19">
         <v>93.3</v>
       </c>
-      <c r="K19">
+      <c r="L19">
         <v>92.5</v>
       </c>
-      <c r="L19">
+      <c r="M19">
         <v>90</v>
       </c>
-      <c r="M19">
-        <v>100</v>
-      </c>
       <c r="N19">
         <v>100</v>
       </c>
       <c r="O19">
+        <v>100</v>
+      </c>
+      <c r="P19">
         <v>95</v>
       </c>
-      <c r="P19">
-        <v>100</v>
-      </c>
       <c r="Q19">
+        <v>100</v>
+      </c>
+      <c r="R19">
+        <v>100</v>
+      </c>
+      <c r="S19">
         <v>95.8</v>
       </c>
-      <c r="R19">
+      <c r="T19">
         <v>95.3</v>
       </c>
-      <c r="S19">
+      <c r="U19">
         <v>93.8</v>
       </c>
-      <c r="T19">
-        <v>100</v>
-      </c>
-      <c r="U19">
+      <c r="V19">
+        <v>100</v>
+      </c>
+      <c r="W19">
         <v>97.90000000000001</v>
       </c>
-      <c r="V19">
+      <c r="X19">
         <v>96.90000000000001</v>
       </c>
-    </row>
-    <row r="20" spans="1:22">
+      <c r="Y19">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25">
       <c r="A20" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B20">
         <v>90</v>
@@ -5474,51 +6114,60 @@
         <v>100</v>
       </c>
       <c r="I20">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="J20">
         <v>90</v>
       </c>
       <c r="K20">
+        <v>90</v>
+      </c>
+      <c r="L20">
         <v>85</v>
       </c>
-      <c r="L20">
+      <c r="M20">
         <v>83.3</v>
       </c>
-      <c r="M20">
+      <c r="N20">
         <v>87.5</v>
       </c>
-      <c r="N20">
+      <c r="O20">
         <v>93.8</v>
       </c>
-      <c r="O20">
+      <c r="P20">
         <v>90</v>
       </c>
-      <c r="P20">
+      <c r="Q20">
+        <v>100</v>
+      </c>
+      <c r="R20">
         <v>93.3</v>
       </c>
-      <c r="Q20">
+      <c r="S20">
         <v>87.5</v>
       </c>
-      <c r="R20">
+      <c r="T20">
         <v>87.5</v>
-      </c>
-      <c r="S20">
-        <v>89.59999999999999</v>
-      </c>
-      <c r="T20">
-        <v>90</v>
       </c>
       <c r="U20">
         <v>89.59999999999999</v>
       </c>
       <c r="V20">
+        <v>90</v>
+      </c>
+      <c r="W20">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="X20">
         <v>93.8</v>
       </c>
-    </row>
-    <row r="21" spans="1:22">
+      <c r="Y20">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25">
       <c r="A21" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B21">
         <v>90</v>
@@ -5542,7 +6191,7 @@
         <v>100</v>
       </c>
       <c r="I21">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="J21">
         <v>90</v>
@@ -5554,39 +6203,48 @@
         <v>90</v>
       </c>
       <c r="M21">
+        <v>90</v>
+      </c>
+      <c r="N21">
         <v>87.5</v>
       </c>
-      <c r="N21">
+      <c r="O21">
         <v>93.8</v>
       </c>
-      <c r="O21">
+      <c r="P21">
         <v>90</v>
       </c>
-      <c r="P21">
+      <c r="Q21">
+        <v>100</v>
+      </c>
+      <c r="R21">
         <v>93.3</v>
       </c>
-      <c r="Q21">
+      <c r="S21">
         <v>87.5</v>
       </c>
-      <c r="R21">
+      <c r="T21">
         <v>90.59999999999999</v>
       </c>
-      <c r="S21">
+      <c r="U21">
         <v>93.8</v>
       </c>
-      <c r="T21">
+      <c r="V21">
         <v>90</v>
       </c>
-      <c r="U21">
+      <c r="W21">
         <v>89.59999999999999</v>
       </c>
-      <c r="V21">
+      <c r="X21">
         <v>93.8</v>
       </c>
-    </row>
-    <row r="22" spans="1:22">
+      <c r="Y21">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25">
       <c r="A22" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B22">
         <v>100</v>
@@ -5613,14 +6271,14 @@
         <v>100</v>
       </c>
       <c r="J22">
+        <v>100</v>
+      </c>
+      <c r="K22">
         <v>93.3</v>
       </c>
-      <c r="K22">
+      <c r="L22">
         <v>97.5</v>
       </c>
-      <c r="L22">
-        <v>100</v>
-      </c>
       <c r="M22">
         <v>100</v>
       </c>
@@ -5634,27 +6292,36 @@
         <v>100</v>
       </c>
       <c r="Q22">
+        <v>100</v>
+      </c>
+      <c r="R22">
+        <v>100</v>
+      </c>
+      <c r="S22">
         <v>91.7</v>
       </c>
-      <c r="R22">
+      <c r="T22">
         <v>96.90000000000001</v>
       </c>
-      <c r="S22">
-        <v>100</v>
-      </c>
-      <c r="T22">
+      <c r="U22">
+        <v>100</v>
+      </c>
+      <c r="V22">
         <v>98.3</v>
       </c>
-      <c r="U22">
+      <c r="W22">
         <v>93.8</v>
       </c>
-      <c r="V22">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="23" spans="1:22">
+      <c r="X22">
+        <v>100</v>
+      </c>
+      <c r="Y22">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25">
       <c r="A23" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B23">
         <v>100</v>
@@ -5699,30 +6366,39 @@
         <v>100</v>
       </c>
       <c r="P23">
+        <v>100</v>
+      </c>
+      <c r="Q23">
+        <v>100</v>
+      </c>
+      <c r="R23">
         <v>96.7</v>
       </c>
-      <c r="Q23">
-        <v>100</v>
-      </c>
-      <c r="R23">
+      <c r="S23">
+        <v>100</v>
+      </c>
+      <c r="T23">
         <v>98.40000000000001</v>
       </c>
-      <c r="S23">
-        <v>100</v>
-      </c>
-      <c r="T23">
-        <v>100</v>
-      </c>
       <c r="U23">
+        <v>100</v>
+      </c>
+      <c r="V23">
+        <v>100</v>
+      </c>
+      <c r="W23">
         <v>97.90000000000001</v>
       </c>
-      <c r="V23">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="24" spans="1:22">
+      <c r="X23">
+        <v>100</v>
+      </c>
+      <c r="Y23">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25">
       <c r="A24" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B24">
         <v>100</v>
@@ -5761,11 +6437,11 @@
         <v>100</v>
       </c>
       <c r="N24">
+        <v>100</v>
+      </c>
+      <c r="O24">
         <v>96.90000000000001</v>
       </c>
-      <c r="O24">
-        <v>100</v>
-      </c>
       <c r="P24">
         <v>100</v>
       </c>
@@ -5782,15 +6458,24 @@
         <v>100</v>
       </c>
       <c r="U24">
+        <v>100</v>
+      </c>
+      <c r="V24">
+        <v>100</v>
+      </c>
+      <c r="W24">
         <v>97.90000000000001</v>
       </c>
-      <c r="V24">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22">
+      <c r="X24">
+        <v>100</v>
+      </c>
+      <c r="Y24">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25">
       <c r="A25" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B25">
         <v>80</v>
@@ -5814,51 +6499,60 @@
         <v>85</v>
       </c>
       <c r="I25">
+        <v>100</v>
+      </c>
+      <c r="J25">
         <v>50</v>
       </c>
-      <c r="J25">
+      <c r="K25">
         <v>86.7</v>
       </c>
-      <c r="K25">
+      <c r="L25">
         <v>27.5</v>
       </c>
-      <c r="L25">
+      <c r="M25">
         <v>66.7</v>
       </c>
-      <c r="M25">
+      <c r="N25">
         <v>0</v>
       </c>
-      <c r="N25">
+      <c r="O25">
         <v>53.1</v>
       </c>
-      <c r="O25">
+      <c r="P25">
         <v>62.5</v>
       </c>
-      <c r="P25">
+      <c r="Q25">
+        <v>100</v>
+      </c>
+      <c r="R25">
         <v>33.3</v>
       </c>
-      <c r="Q25">
+      <c r="S25">
         <v>54.2</v>
       </c>
-      <c r="R25">
+      <c r="T25">
         <v>17.2</v>
       </c>
-      <c r="S25">
+      <c r="U25">
         <v>41.7</v>
       </c>
-      <c r="T25">
+      <c r="V25">
         <v>0</v>
       </c>
-      <c r="U25">
+      <c r="W25">
         <v>35.4</v>
       </c>
-      <c r="V25">
+      <c r="X25">
         <v>39.1</v>
       </c>
-    </row>
-    <row r="26" spans="1:22">
+      <c r="Y25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25">
       <c r="A26" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B26">
         <v>100</v>
@@ -5885,48 +6579,57 @@
         <v>100</v>
       </c>
       <c r="J26">
+        <v>100</v>
+      </c>
+      <c r="K26">
         <v>90</v>
       </c>
-      <c r="K26">
+      <c r="L26">
         <v>97.5</v>
       </c>
-      <c r="L26">
-        <v>100</v>
-      </c>
       <c r="M26">
         <v>100</v>
       </c>
       <c r="N26">
+        <v>100</v>
+      </c>
+      <c r="O26">
         <v>93.8</v>
       </c>
-      <c r="O26">
+      <c r="P26">
         <v>97.5</v>
       </c>
-      <c r="P26">
-        <v>100</v>
-      </c>
       <c r="Q26">
+        <v>100</v>
+      </c>
+      <c r="R26">
+        <v>100</v>
+      </c>
+      <c r="S26">
         <v>93.8</v>
       </c>
-      <c r="R26">
+      <c r="T26">
         <v>98.40000000000001</v>
       </c>
-      <c r="S26">
-        <v>100</v>
-      </c>
-      <c r="T26">
+      <c r="U26">
+        <v>100</v>
+      </c>
+      <c r="V26">
         <v>96.7</v>
       </c>
-      <c r="U26">
+      <c r="W26">
         <v>95.8</v>
       </c>
-      <c r="V26">
+      <c r="X26">
         <v>98.40000000000001</v>
       </c>
-    </row>
-    <row r="27" spans="1:22">
+      <c r="Y26">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25">
       <c r="A27" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B27">
         <v>100</v>
@@ -5953,11 +6656,11 @@
         <v>100</v>
       </c>
       <c r="J27">
+        <v>100</v>
+      </c>
+      <c r="K27">
         <v>93.3</v>
       </c>
-      <c r="K27">
-        <v>100</v>
-      </c>
       <c r="L27">
         <v>100</v>
       </c>
@@ -5965,36 +6668,45 @@
         <v>100</v>
       </c>
       <c r="N27">
+        <v>100</v>
+      </c>
+      <c r="O27">
         <v>96.90000000000001</v>
       </c>
-      <c r="O27">
+      <c r="P27">
         <v>97.5</v>
       </c>
-      <c r="P27">
-        <v>100</v>
-      </c>
       <c r="Q27">
+        <v>100</v>
+      </c>
+      <c r="R27">
+        <v>100</v>
+      </c>
+      <c r="S27">
         <v>95.8</v>
       </c>
-      <c r="R27">
-        <v>100</v>
-      </c>
-      <c r="S27">
-        <v>100</v>
-      </c>
       <c r="T27">
         <v>100</v>
       </c>
       <c r="U27">
+        <v>100</v>
+      </c>
+      <c r="V27">
+        <v>100</v>
+      </c>
+      <c r="W27">
         <v>97.90000000000001</v>
       </c>
-      <c r="V27">
+      <c r="X27">
         <v>98.40000000000001</v>
       </c>
-    </row>
-    <row r="28" spans="1:22">
+      <c r="Y27">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25">
       <c r="A28" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B28">
         <v>100</v>
@@ -6018,51 +6730,60 @@
         <v>85</v>
       </c>
       <c r="I28">
+        <v>100</v>
+      </c>
+      <c r="J28">
         <v>95</v>
       </c>
-      <c r="J28">
-        <v>100</v>
-      </c>
       <c r="K28">
+        <v>100</v>
+      </c>
+      <c r="L28">
         <v>92.5</v>
       </c>
-      <c r="L28">
+      <c r="M28">
         <v>96.7</v>
       </c>
-      <c r="M28">
+      <c r="N28">
         <v>95</v>
       </c>
-      <c r="N28">
+      <c r="O28">
         <v>93.8</v>
       </c>
-      <c r="O28">
+      <c r="P28">
         <v>82.5</v>
       </c>
-      <c r="P28">
+      <c r="Q28">
+        <v>100</v>
+      </c>
+      <c r="R28">
         <v>93.3</v>
       </c>
-      <c r="Q28">
-        <v>100</v>
-      </c>
-      <c r="R28">
+      <c r="S28">
+        <v>100</v>
+      </c>
+      <c r="T28">
         <v>93.8</v>
       </c>
-      <c r="S28">
+      <c r="U28">
         <v>97.90000000000001</v>
       </c>
-      <c r="T28">
+      <c r="V28">
         <v>96.7</v>
       </c>
-      <c r="U28">
+      <c r="W28">
         <v>89.59999999999999</v>
       </c>
-      <c r="V28">
+      <c r="X28">
         <v>89.09999999999999</v>
       </c>
-    </row>
-    <row r="29" spans="1:22">
+      <c r="Y28">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25">
       <c r="A29" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B29">
         <v>100</v>
@@ -6086,51 +6807,60 @@
         <v>100</v>
       </c>
       <c r="I29">
+        <v>100</v>
+      </c>
+      <c r="J29">
         <v>95</v>
       </c>
-      <c r="J29">
-        <v>100</v>
-      </c>
       <c r="K29">
+        <v>100</v>
+      </c>
+      <c r="L29">
         <v>85</v>
       </c>
-      <c r="L29">
+      <c r="M29">
         <v>96.7</v>
       </c>
-      <c r="M29">
+      <c r="N29">
         <v>97.5</v>
       </c>
-      <c r="N29">
-        <v>100</v>
-      </c>
       <c r="O29">
+        <v>100</v>
+      </c>
+      <c r="P29">
         <v>95</v>
       </c>
-      <c r="P29">
+      <c r="Q29">
+        <v>100</v>
+      </c>
+      <c r="R29">
         <v>93.3</v>
       </c>
-      <c r="Q29">
-        <v>100</v>
-      </c>
-      <c r="R29">
+      <c r="S29">
+        <v>100</v>
+      </c>
+      <c r="T29">
         <v>89.09999999999999</v>
       </c>
-      <c r="S29">
+      <c r="U29">
         <v>95.8</v>
       </c>
-      <c r="T29">
+      <c r="V29">
         <v>98.3</v>
       </c>
-      <c r="U29">
-        <v>100</v>
-      </c>
-      <c r="V29">
+      <c r="W29">
+        <v>100</v>
+      </c>
+      <c r="X29">
         <v>96.90000000000001</v>
       </c>
-    </row>
-    <row r="30" spans="1:22">
+      <c r="Y29">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25">
       <c r="A30" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B30">
         <v>100</v>
@@ -6172,11 +6902,11 @@
         <v>100</v>
       </c>
       <c r="O30">
+        <v>100</v>
+      </c>
+      <c r="P30">
         <v>95</v>
       </c>
-      <c r="P30">
-        <v>100</v>
-      </c>
       <c r="Q30">
         <v>100</v>
       </c>
@@ -6190,15 +6920,24 @@
         <v>100</v>
       </c>
       <c r="U30">
+        <v>100</v>
+      </c>
+      <c r="V30">
+        <v>100</v>
+      </c>
+      <c r="W30">
         <v>97.90000000000001</v>
       </c>
-      <c r="V30">
+      <c r="X30">
         <v>96.90000000000001</v>
       </c>
-    </row>
-    <row r="31" spans="1:22">
+      <c r="Y30">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25">
       <c r="A31" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B31">
         <v>100</v>
@@ -6243,30 +6982,39 @@
         <v>100</v>
       </c>
       <c r="P31">
+        <v>100</v>
+      </c>
+      <c r="Q31">
+        <v>100</v>
+      </c>
+      <c r="R31">
         <v>96.7</v>
       </c>
-      <c r="Q31">
+      <c r="S31">
         <v>93.8</v>
       </c>
-      <c r="R31">
+      <c r="T31">
         <v>98.40000000000001</v>
       </c>
-      <c r="S31">
+      <c r="U31">
         <v>97.90000000000001</v>
       </c>
-      <c r="T31">
-        <v>100</v>
-      </c>
-      <c r="U31">
+      <c r="V31">
+        <v>100</v>
+      </c>
+      <c r="W31">
         <v>93.8</v>
       </c>
-      <c r="V31">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="32" spans="1:22">
+      <c r="X31">
+        <v>100</v>
+      </c>
+      <c r="Y31">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25">
       <c r="A32" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B32">
         <v>90</v>
@@ -6290,51 +7038,60 @@
         <v>95</v>
       </c>
       <c r="I32">
+        <v>100</v>
+      </c>
+      <c r="J32">
         <v>95</v>
       </c>
-      <c r="J32">
-        <v>100</v>
-      </c>
       <c r="K32">
         <v>100</v>
       </c>
       <c r="L32">
+        <v>100</v>
+      </c>
+      <c r="M32">
         <v>93.3</v>
       </c>
-      <c r="M32">
+      <c r="N32">
         <v>95</v>
       </c>
-      <c r="N32">
+      <c r="O32">
         <v>93.8</v>
       </c>
-      <c r="O32">
+      <c r="P32">
         <v>97.5</v>
       </c>
-      <c r="P32">
+      <c r="Q32">
+        <v>100</v>
+      </c>
+      <c r="R32">
         <v>96.7</v>
       </c>
-      <c r="Q32">
+      <c r="S32">
         <v>97.90000000000001</v>
       </c>
-      <c r="R32">
-        <v>100</v>
-      </c>
-      <c r="S32">
+      <c r="T32">
+        <v>100</v>
+      </c>
+      <c r="U32">
         <v>95.8</v>
       </c>
-      <c r="T32">
+      <c r="V32">
         <v>96.7</v>
       </c>
-      <c r="U32">
+      <c r="W32">
         <v>93.8</v>
       </c>
-      <c r="V32">
+      <c r="X32">
         <v>98.40000000000001</v>
       </c>
-    </row>
-    <row r="33" spans="1:22">
+      <c r="Y32">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25">
       <c r="A33" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B33">
         <v>100</v>
@@ -6376,33 +7133,42 @@
         <v>100</v>
       </c>
       <c r="O33">
+        <v>100</v>
+      </c>
+      <c r="P33">
         <v>97.5</v>
       </c>
-      <c r="P33">
-        <v>100</v>
-      </c>
       <c r="Q33">
+        <v>100</v>
+      </c>
+      <c r="R33">
+        <v>100</v>
+      </c>
+      <c r="S33">
         <v>97.90000000000001</v>
       </c>
-      <c r="R33">
+      <c r="T33">
         <v>98.40000000000001</v>
       </c>
-      <c r="S33">
-        <v>100</v>
-      </c>
-      <c r="T33">
-        <v>100</v>
-      </c>
       <c r="U33">
+        <v>100</v>
+      </c>
+      <c r="V33">
+        <v>100</v>
+      </c>
+      <c r="W33">
         <v>93.8</v>
       </c>
-      <c r="V33">
+      <c r="X33">
         <v>95.3</v>
       </c>
-    </row>
-    <row r="34" spans="1:22">
+      <c r="Y33">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25">
       <c r="A34" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B34">
         <v>100</v>
@@ -6444,33 +7210,42 @@
         <v>100</v>
       </c>
       <c r="O34">
+        <v>100</v>
+      </c>
+      <c r="P34">
         <v>95</v>
       </c>
-      <c r="P34">
+      <c r="Q34">
+        <v>100</v>
+      </c>
+      <c r="R34">
         <v>96.7</v>
       </c>
-      <c r="Q34">
-        <v>100</v>
-      </c>
-      <c r="R34">
+      <c r="S34">
+        <v>100</v>
+      </c>
+      <c r="T34">
         <v>98.40000000000001</v>
       </c>
-      <c r="S34">
-        <v>100</v>
-      </c>
-      <c r="T34">
-        <v>100</v>
-      </c>
       <c r="U34">
         <v>100</v>
       </c>
       <c r="V34">
+        <v>100</v>
+      </c>
+      <c r="W34">
+        <v>100</v>
+      </c>
+      <c r="X34">
         <v>96.90000000000001</v>
       </c>
-    </row>
-    <row r="35" spans="1:22">
+      <c r="Y34">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25">
       <c r="A35" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B35">
         <v>90</v>
@@ -6494,11 +7269,11 @@
         <v>100</v>
       </c>
       <c r="I35">
+        <v>100</v>
+      </c>
+      <c r="J35">
         <v>95</v>
       </c>
-      <c r="J35">
-        <v>100</v>
-      </c>
       <c r="K35">
         <v>100</v>
       </c>
@@ -6515,14 +7290,14 @@
         <v>100</v>
       </c>
       <c r="P35">
+        <v>100</v>
+      </c>
+      <c r="Q35">
+        <v>100</v>
+      </c>
+      <c r="R35">
         <v>96.7</v>
       </c>
-      <c r="Q35">
-        <v>100</v>
-      </c>
-      <c r="R35">
-        <v>100</v>
-      </c>
       <c r="S35">
         <v>100</v>
       </c>
@@ -6530,15 +7305,24 @@
         <v>100</v>
       </c>
       <c r="U35">
+        <v>100</v>
+      </c>
+      <c r="V35">
+        <v>100</v>
+      </c>
+      <c r="W35">
         <v>97.90000000000001</v>
       </c>
-      <c r="V35">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="36" spans="1:22">
+      <c r="X35">
+        <v>100</v>
+      </c>
+      <c r="Y35">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25">
       <c r="A36" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B36">
         <v>100</v>
@@ -6603,10 +7387,19 @@
       <c r="V36">
         <v>100</v>
       </c>
-    </row>
-    <row r="37" spans="1:22">
+      <c r="W36">
+        <v>100</v>
+      </c>
+      <c r="X36">
+        <v>100</v>
+      </c>
+      <c r="Y36">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25">
       <c r="A37" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B37">
         <v>100</v>
@@ -6636,45 +7429,54 @@
         <v>100</v>
       </c>
       <c r="K37">
+        <v>100</v>
+      </c>
+      <c r="L37">
         <v>92.5</v>
       </c>
-      <c r="L37">
+      <c r="M37">
         <v>90</v>
       </c>
-      <c r="M37">
-        <v>100</v>
-      </c>
       <c r="N37">
+        <v>100</v>
+      </c>
+      <c r="O37">
         <v>93.8</v>
       </c>
-      <c r="O37">
+      <c r="P37">
         <v>82.5</v>
       </c>
-      <c r="P37">
-        <v>100</v>
-      </c>
       <c r="Q37">
-        <v>93.8</v>
+        <v>100</v>
       </c>
       <c r="R37">
-        <v>93.8</v>
+        <v>100</v>
       </c>
       <c r="S37">
         <v>93.8</v>
       </c>
       <c r="T37">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="U37">
+        <v>93.8</v>
+      </c>
+      <c r="V37">
+        <v>100</v>
+      </c>
+      <c r="W37">
         <v>95.8</v>
       </c>
-      <c r="V37">
+      <c r="X37">
         <v>89.09999999999999</v>
       </c>
-    </row>
-    <row r="38" spans="1:22">
+      <c r="Y37">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25">
       <c r="A38" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B38">
         <v>100</v>
@@ -6698,17 +7500,17 @@
         <v>100</v>
       </c>
       <c r="I38">
+        <v>100</v>
+      </c>
+      <c r="J38">
         <v>95</v>
       </c>
-      <c r="J38">
+      <c r="K38">
         <v>93.3</v>
       </c>
-      <c r="K38">
+      <c r="L38">
         <v>95</v>
       </c>
-      <c r="L38">
-        <v>100</v>
-      </c>
       <c r="M38">
         <v>100</v>
       </c>
@@ -6716,33 +7518,42 @@
         <v>100</v>
       </c>
       <c r="O38">
+        <v>100</v>
+      </c>
+      <c r="P38">
         <v>95</v>
       </c>
-      <c r="P38">
+      <c r="Q38">
+        <v>100</v>
+      </c>
+      <c r="R38">
         <v>96.7</v>
       </c>
-      <c r="Q38">
+      <c r="S38">
         <v>95.8</v>
       </c>
-      <c r="R38">
+      <c r="T38">
         <v>96.90000000000001</v>
       </c>
-      <c r="S38">
-        <v>100</v>
-      </c>
-      <c r="T38">
-        <v>100</v>
-      </c>
       <c r="U38">
         <v>100</v>
       </c>
       <c r="V38">
+        <v>100</v>
+      </c>
+      <c r="W38">
+        <v>100</v>
+      </c>
+      <c r="X38">
         <v>96.90000000000001</v>
       </c>
-    </row>
-    <row r="39" spans="1:22">
+      <c r="Y38">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25">
       <c r="A39" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B39">
         <v>90</v>
@@ -6766,11 +7577,11 @@
         <v>100</v>
       </c>
       <c r="I39">
+        <v>100</v>
+      </c>
+      <c r="J39">
         <v>95</v>
       </c>
-      <c r="J39">
-        <v>100</v>
-      </c>
       <c r="K39">
         <v>100</v>
       </c>
@@ -6784,17 +7595,17 @@
         <v>100</v>
       </c>
       <c r="O39">
+        <v>100</v>
+      </c>
+      <c r="P39">
         <v>95</v>
       </c>
-      <c r="P39">
+      <c r="Q39">
+        <v>100</v>
+      </c>
+      <c r="R39">
         <v>96.7</v>
       </c>
-      <c r="Q39">
-        <v>100</v>
-      </c>
-      <c r="R39">
-        <v>100</v>
-      </c>
       <c r="S39">
         <v>100</v>
       </c>
@@ -6802,15 +7613,24 @@
         <v>100</v>
       </c>
       <c r="U39">
+        <v>100</v>
+      </c>
+      <c r="V39">
+        <v>100</v>
+      </c>
+      <c r="W39">
         <v>97.90000000000001</v>
       </c>
-      <c r="V39">
+      <c r="X39">
         <v>96.90000000000001</v>
       </c>
-    </row>
-    <row r="40" spans="1:22">
+      <c r="Y39">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25">
       <c r="A40" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B40">
         <v>100</v>
@@ -6849,36 +7669,45 @@
         <v>100</v>
       </c>
       <c r="N40">
+        <v>100</v>
+      </c>
+      <c r="O40">
         <v>96.90000000000001</v>
       </c>
-      <c r="O40">
+      <c r="P40">
         <v>97.5</v>
       </c>
-      <c r="P40">
-        <v>100</v>
-      </c>
       <c r="Q40">
         <v>100</v>
       </c>
       <c r="R40">
+        <v>100</v>
+      </c>
+      <c r="S40">
+        <v>100</v>
+      </c>
+      <c r="T40">
         <v>98.40000000000001</v>
       </c>
-      <c r="S40">
-        <v>100</v>
-      </c>
-      <c r="T40">
-        <v>100</v>
-      </c>
       <c r="U40">
+        <v>100</v>
+      </c>
+      <c r="V40">
+        <v>100</v>
+      </c>
+      <c r="W40">
         <v>97.90000000000001</v>
       </c>
-      <c r="V40">
+      <c r="X40">
         <v>98.40000000000001</v>
       </c>
-    </row>
-    <row r="41" spans="1:22">
+      <c r="Y40">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25">
       <c r="A41" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B41">
         <v>100</v>
@@ -6943,10 +7772,19 @@
       <c r="V41">
         <v>100</v>
       </c>
-    </row>
-    <row r="42" spans="1:22">
+      <c r="W41">
+        <v>100</v>
+      </c>
+      <c r="X41">
+        <v>100</v>
+      </c>
+      <c r="Y41">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25">
       <c r="A42" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B42">
         <v>100</v>
@@ -7009,14 +7847,23 @@
         <v>100</v>
       </c>
       <c r="V42">
+        <v>100</v>
+      </c>
+      <c r="W42">
+        <v>100</v>
+      </c>
+      <c r="X42">
+        <v>100</v>
+      </c>
+      <c r="Y42">
         <v>100</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="I1:O1"/>
-    <mergeCell ref="P1:V1"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="J1:Q1"/>
+    <mergeCell ref="R1:Y1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7037,31 +7884,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -7290,21 +8137,33 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>64</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
         <v>72</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
+      <c r="F9" s="2">
+        <v>100</v>
+      </c>
+      <c r="G9" s="2">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>10</v>
+      </c>
       <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7339,7 +8198,7 @@
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -7373,7 +8232,7 @@
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>

--- a/grupos/1EM - Estadisticos 20231.xlsx
+++ b/grupos/1EM - Estadisticos 20231.xlsx
@@ -860,7 +860,7 @@
         <v>10</v>
       </c>
       <c r="Z4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA4">
         <v>5</v>
@@ -869,16 +869,16 @@
         <v>5</v>
       </c>
       <c r="AC4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD4">
         <v>5</v>
       </c>
       <c r="AE4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AF4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG4">
         <v>10</v>
@@ -961,7 +961,7 @@
         <v>10</v>
       </c>
       <c r="Z5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA5">
         <v>10</v>
@@ -970,10 +970,10 @@
         <v>10</v>
       </c>
       <c r="AC5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE5">
         <v>10</v>
@@ -1062,22 +1062,22 @@
         <v>10</v>
       </c>
       <c r="Z6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB6">
         <v>5</v>
       </c>
       <c r="AC6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD6">
         <v>5</v>
       </c>
       <c r="AE6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF6">
         <v>5</v>
@@ -1166,22 +1166,22 @@
         <v>10</v>
       </c>
       <c r="AA7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC7">
         <v>10</v>
       </c>
       <c r="AD7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE7">
         <v>10</v>
       </c>
       <c r="AF7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG7">
         <v>10</v>
@@ -1267,10 +1267,10 @@
         <v>10</v>
       </c>
       <c r="AA8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC8">
         <v>10</v>
@@ -1368,22 +1368,22 @@
         <v>10</v>
       </c>
       <c r="AA9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD9">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE9">
         <v>10</v>
       </c>
       <c r="AF9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG9">
         <v>10</v>
@@ -1466,25 +1466,25 @@
         <v>10</v>
       </c>
       <c r="Z10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD10">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE10">
         <v>10</v>
       </c>
       <c r="AF10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG10">
         <v>10</v>
@@ -1582,7 +1582,7 @@
         <v>5</v>
       </c>
       <c r="AE11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF11">
         <v>5</v>
@@ -1668,7 +1668,7 @@
         <v>10</v>
       </c>
       <c r="Z12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA12">
         <v>5</v>
@@ -1677,7 +1677,7 @@
         <v>5</v>
       </c>
       <c r="AC12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD12">
         <v>5</v>
@@ -1686,7 +1686,7 @@
         <v>5</v>
       </c>
       <c r="AF12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG12">
         <v>10</v>
@@ -1769,25 +1769,25 @@
         <v>10</v>
       </c>
       <c r="Z13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG13">
         <v>10</v>
@@ -1873,22 +1873,22 @@
         <v>10</v>
       </c>
       <c r="AA14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG14">
         <v>10</v>
@@ -1971,19 +1971,19 @@
         <v>10</v>
       </c>
       <c r="Z15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE15">
         <v>10</v>
@@ -2072,25 +2072,25 @@
         <v>10</v>
       </c>
       <c r="Z16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD16">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE16">
         <v>10</v>
       </c>
       <c r="AF16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG16">
         <v>10</v>
@@ -2176,22 +2176,22 @@
         <v>10</v>
       </c>
       <c r="AA17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC17">
         <v>10</v>
       </c>
       <c r="AD17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE17">
         <v>10</v>
       </c>
       <c r="AF17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG17">
         <v>10</v>
@@ -2274,25 +2274,25 @@
         <v>10</v>
       </c>
       <c r="Z18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD18">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE18">
         <v>10</v>
       </c>
       <c r="AF18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG18">
         <v>10</v>
@@ -2375,25 +2375,25 @@
         <v>10</v>
       </c>
       <c r="Z19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG19">
         <v>10</v>
@@ -2476,7 +2476,7 @@
         <v>10</v>
       </c>
       <c r="Z20">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA20">
         <v>5</v>
@@ -2485,16 +2485,16 @@
         <v>5</v>
       </c>
       <c r="AC20">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD20">
         <v>5</v>
       </c>
       <c r="AE20">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF20">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG20">
         <v>10</v>
@@ -2577,7 +2577,7 @@
         <v>10</v>
       </c>
       <c r="Z21">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA21">
         <v>5</v>
@@ -2586,16 +2586,16 @@
         <v>5</v>
       </c>
       <c r="AC21">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD21">
         <v>5</v>
       </c>
       <c r="AE21">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF21">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG21">
         <v>10</v>
@@ -2678,25 +2678,25 @@
         <v>10</v>
       </c>
       <c r="Z22">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA22">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB22">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC22">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD22">
         <v>5</v>
       </c>
       <c r="AE22">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF22">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG22">
         <v>10</v>
@@ -2779,25 +2779,25 @@
         <v>10</v>
       </c>
       <c r="Z23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA23">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD23">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE23">
         <v>10</v>
       </c>
       <c r="AF23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG23">
         <v>10</v>
@@ -2883,7 +2883,7 @@
         <v>10</v>
       </c>
       <c r="AA24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB24">
         <v>10</v>
@@ -2892,7 +2892,7 @@
         <v>10</v>
       </c>
       <c r="AD24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE24">
         <v>10</v>
@@ -3085,16 +3085,16 @@
         <v>10</v>
       </c>
       <c r="AA26">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD26">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE26">
         <v>10</v>
@@ -3186,22 +3186,22 @@
         <v>10</v>
       </c>
       <c r="AA27">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB27">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC27">
         <v>10</v>
       </c>
       <c r="AD27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE27">
         <v>10</v>
       </c>
       <c r="AF27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG27">
         <v>10</v>
@@ -3284,25 +3284,25 @@
         <v>10</v>
       </c>
       <c r="Z28">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA28">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB28">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC28">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD28">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG28">
         <v>10</v>
@@ -3385,25 +3385,25 @@
         <v>10</v>
       </c>
       <c r="Z29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC29">
         <v>10</v>
       </c>
       <c r="AD29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE29">
         <v>10</v>
       </c>
       <c r="AF29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG29">
         <v>10</v>
@@ -3486,25 +3486,25 @@
         <v>10</v>
       </c>
       <c r="Z30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD30">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE30">
         <v>10</v>
       </c>
       <c r="AF30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG30">
         <v>10</v>
@@ -3587,25 +3587,25 @@
         <v>10</v>
       </c>
       <c r="Z31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA31">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB31">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD31">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF31">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG31">
         <v>10</v>
@@ -3688,25 +3688,25 @@
         <v>10</v>
       </c>
       <c r="Z32">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA32">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB32">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC32">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD32">
         <v>5</v>
       </c>
       <c r="AE32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF32">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG32">
         <v>10</v>
@@ -3789,25 +3789,25 @@
         <v>10</v>
       </c>
       <c r="Z33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA33">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB33">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC33">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD33">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE33">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF33">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG33">
         <v>10</v>
@@ -3890,25 +3890,25 @@
         <v>10</v>
       </c>
       <c r="Z34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA34">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD34">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE34">
         <v>10</v>
       </c>
       <c r="AF34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG34">
         <v>10</v>
@@ -3991,25 +3991,25 @@
         <v>10</v>
       </c>
       <c r="Z35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA35">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB35">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC35">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD35">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF35">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG35">
         <v>10</v>
@@ -4092,25 +4092,25 @@
         <v>10</v>
       </c>
       <c r="Z36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA36">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB36">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD36">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE36">
         <v>10</v>
       </c>
       <c r="AF36">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG36">
         <v>10</v>
@@ -4193,25 +4193,25 @@
         <v>10</v>
       </c>
       <c r="Z37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA37">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB37">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD37">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE37">
         <v>10</v>
       </c>
       <c r="AF37">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG37">
         <v>10</v>
@@ -4294,25 +4294,25 @@
         <v>10</v>
       </c>
       <c r="Z38">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA38">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB38">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC38">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD38">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE38">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF38">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG38">
         <v>10</v>
@@ -4395,25 +4395,25 @@
         <v>10</v>
       </c>
       <c r="Z39">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA39">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB39">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC39">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD39">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE39">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF39">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG39">
         <v>10</v>
@@ -4499,22 +4499,22 @@
         <v>10</v>
       </c>
       <c r="AA40">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB40">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC40">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD40">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE40">
         <v>10</v>
       </c>
       <c r="AF40">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG40">
         <v>10</v>
@@ -4600,16 +4600,16 @@
         <v>10</v>
       </c>
       <c r="AA41">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB41">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC41">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD41">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE41">
         <v>10</v>
@@ -4698,25 +4698,25 @@
         <v>10</v>
       </c>
       <c r="Z42">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA42">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB42">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC42">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD42">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE42">
         <v>10</v>
       </c>
       <c r="AF42">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG42">
         <v>10</v>
@@ -7934,7 +7934,7 @@
         <v>23.1</v>
       </c>
       <c r="H2">
-        <v>6.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -7966,7 +7966,7 @@
         <v>17.9</v>
       </c>
       <c r="H3">
-        <v>7.5</v>
+        <v>9.1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -7998,7 +7998,7 @@
         <v>15.4</v>
       </c>
       <c r="H4">
-        <v>7.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -8030,7 +8030,7 @@
         <v>7.7</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -8062,7 +8062,7 @@
         <v>5.1</v>
       </c>
       <c r="H6">
-        <v>8.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -8094,7 +8094,7 @@
         <v>5.1</v>
       </c>
       <c r="H7">
-        <v>8.300000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -8126,7 +8126,7 @@
         <v>5.1</v>
       </c>
       <c r="H8">
-        <v>9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I8">
         <v>0</v>

--- a/grupos/1EM - Estadisticos 20231.xlsx
+++ b/grupos/1EM - Estadisticos 20231.xlsx
@@ -860,7 +860,7 @@
         <v>10</v>
       </c>
       <c r="Z4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA4">
         <v>5</v>
@@ -869,16 +869,16 @@
         <v>5</v>
       </c>
       <c r="AC4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD4">
         <v>5</v>
       </c>
       <c r="AE4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AF4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG4">
         <v>10</v>
@@ -961,7 +961,7 @@
         <v>10</v>
       </c>
       <c r="Z5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA5">
         <v>10</v>
@@ -970,10 +970,10 @@
         <v>10</v>
       </c>
       <c r="AC5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE5">
         <v>10</v>
@@ -1062,22 +1062,22 @@
         <v>10</v>
       </c>
       <c r="Z6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA6">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB6">
         <v>5</v>
       </c>
       <c r="AC6">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD6">
         <v>5</v>
       </c>
       <c r="AE6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF6">
         <v>5</v>
@@ -1166,22 +1166,22 @@
         <v>10</v>
       </c>
       <c r="AA7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC7">
         <v>10</v>
       </c>
       <c r="AD7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE7">
         <v>10</v>
       </c>
       <c r="AF7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG7">
         <v>10</v>
@@ -1267,10 +1267,10 @@
         <v>10</v>
       </c>
       <c r="AA8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC8">
         <v>10</v>
@@ -1368,22 +1368,22 @@
         <v>10</v>
       </c>
       <c r="AA9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD9">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE9">
         <v>10</v>
       </c>
       <c r="AF9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG9">
         <v>10</v>
@@ -1466,25 +1466,25 @@
         <v>10</v>
       </c>
       <c r="Z10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD10">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE10">
         <v>10</v>
       </c>
       <c r="AF10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG10">
         <v>10</v>
@@ -1582,7 +1582,7 @@
         <v>5</v>
       </c>
       <c r="AE11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF11">
         <v>5</v>
@@ -1668,7 +1668,7 @@
         <v>10</v>
       </c>
       <c r="Z12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA12">
         <v>5</v>
@@ -1677,7 +1677,7 @@
         <v>5</v>
       </c>
       <c r="AC12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD12">
         <v>5</v>
@@ -1686,7 +1686,7 @@
         <v>5</v>
       </c>
       <c r="AF12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG12">
         <v>10</v>
@@ -1769,25 +1769,25 @@
         <v>10</v>
       </c>
       <c r="Z13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG13">
         <v>10</v>
@@ -1873,22 +1873,22 @@
         <v>10</v>
       </c>
       <c r="AA14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG14">
         <v>10</v>
@@ -1971,19 +1971,19 @@
         <v>10</v>
       </c>
       <c r="Z15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE15">
         <v>10</v>
@@ -2072,25 +2072,25 @@
         <v>10</v>
       </c>
       <c r="Z16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD16">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE16">
         <v>10</v>
       </c>
       <c r="AF16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG16">
         <v>10</v>
@@ -2176,22 +2176,22 @@
         <v>10</v>
       </c>
       <c r="AA17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC17">
         <v>10</v>
       </c>
       <c r="AD17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE17">
         <v>10</v>
       </c>
       <c r="AF17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG17">
         <v>10</v>
@@ -2274,25 +2274,25 @@
         <v>10</v>
       </c>
       <c r="Z18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD18">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE18">
         <v>10</v>
       </c>
       <c r="AF18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG18">
         <v>10</v>
@@ -2375,25 +2375,25 @@
         <v>10</v>
       </c>
       <c r="Z19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF19">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG19">
         <v>10</v>
@@ -2476,7 +2476,7 @@
         <v>10</v>
       </c>
       <c r="Z20">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA20">
         <v>5</v>
@@ -2485,16 +2485,16 @@
         <v>5</v>
       </c>
       <c r="AC20">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD20">
         <v>5</v>
       </c>
       <c r="AE20">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF20">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG20">
         <v>10</v>
@@ -2577,7 +2577,7 @@
         <v>10</v>
       </c>
       <c r="Z21">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA21">
         <v>5</v>
@@ -2586,16 +2586,16 @@
         <v>5</v>
       </c>
       <c r="AC21">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD21">
         <v>5</v>
       </c>
       <c r="AE21">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF21">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG21">
         <v>10</v>
@@ -2678,25 +2678,25 @@
         <v>10</v>
       </c>
       <c r="Z22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA22">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB22">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD22">
         <v>5</v>
       </c>
       <c r="AE22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG22">
         <v>10</v>
@@ -2779,25 +2779,25 @@
         <v>10</v>
       </c>
       <c r="Z23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD23">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE23">
         <v>10</v>
       </c>
       <c r="AF23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG23">
         <v>10</v>
@@ -2883,7 +2883,7 @@
         <v>10</v>
       </c>
       <c r="AA24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB24">
         <v>10</v>
@@ -2892,7 +2892,7 @@
         <v>10</v>
       </c>
       <c r="AD24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE24">
         <v>10</v>
@@ -3085,16 +3085,16 @@
         <v>10</v>
       </c>
       <c r="AA26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE26">
         <v>10</v>
@@ -3186,22 +3186,22 @@
         <v>10</v>
       </c>
       <c r="AA27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC27">
         <v>10</v>
       </c>
       <c r="AD27">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE27">
         <v>10</v>
       </c>
       <c r="AF27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG27">
         <v>10</v>
@@ -3284,25 +3284,25 @@
         <v>10</v>
       </c>
       <c r="Z28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA28">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB28">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD28">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG28">
         <v>10</v>
@@ -3385,25 +3385,25 @@
         <v>10</v>
       </c>
       <c r="Z29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC29">
         <v>10</v>
       </c>
       <c r="AD29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE29">
         <v>10</v>
       </c>
       <c r="AF29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG29">
         <v>10</v>
@@ -3486,25 +3486,25 @@
         <v>10</v>
       </c>
       <c r="Z30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA30">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB30">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC30">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD30">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE30">
         <v>10</v>
       </c>
       <c r="AF30">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG30">
         <v>10</v>
@@ -3587,25 +3587,25 @@
         <v>10</v>
       </c>
       <c r="Z31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA31">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD31">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG31">
         <v>10</v>
@@ -3688,25 +3688,25 @@
         <v>10</v>
       </c>
       <c r="Z32">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA32">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB32">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC32">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD32">
         <v>5</v>
       </c>
       <c r="AE32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF32">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG32">
         <v>10</v>
@@ -3789,25 +3789,25 @@
         <v>10</v>
       </c>
       <c r="Z33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA33">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB33">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD33">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF33">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG33">
         <v>10</v>
@@ -3890,25 +3890,25 @@
         <v>10</v>
       </c>
       <c r="Z34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA34">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD34">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE34">
         <v>10</v>
       </c>
       <c r="AF34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG34">
         <v>10</v>
@@ -3991,25 +3991,25 @@
         <v>10</v>
       </c>
       <c r="Z35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA35">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB35">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC35">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD35">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF35">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG35">
         <v>10</v>
@@ -4092,25 +4092,25 @@
         <v>10</v>
       </c>
       <c r="Z36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA36">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB36">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD36">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE36">
         <v>10</v>
       </c>
       <c r="AF36">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG36">
         <v>10</v>
@@ -4193,25 +4193,25 @@
         <v>10</v>
       </c>
       <c r="Z37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA37">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB37">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD37">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE37">
         <v>10</v>
       </c>
       <c r="AF37">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG37">
         <v>10</v>
@@ -4294,25 +4294,25 @@
         <v>10</v>
       </c>
       <c r="Z38">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA38">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB38">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC38">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD38">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE38">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF38">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG38">
         <v>10</v>
@@ -4395,25 +4395,25 @@
         <v>10</v>
       </c>
       <c r="Z39">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA39">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB39">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC39">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD39">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE39">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF39">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG39">
         <v>10</v>
@@ -4499,22 +4499,22 @@
         <v>10</v>
       </c>
       <c r="AA40">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB40">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC40">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD40">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE40">
         <v>10</v>
       </c>
       <c r="AF40">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG40">
         <v>10</v>
@@ -4600,16 +4600,16 @@
         <v>10</v>
       </c>
       <c r="AA41">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB41">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC41">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD41">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE41">
         <v>10</v>
@@ -4698,25 +4698,25 @@
         <v>10</v>
       </c>
       <c r="Z42">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA42">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB42">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC42">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD42">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE42">
         <v>10</v>
       </c>
       <c r="AF42">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG42">
         <v>10</v>
@@ -7934,7 +7934,7 @@
         <v>23.1</v>
       </c>
       <c r="H2">
-        <v>8.800000000000001</v>
+        <v>6.5</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -7966,7 +7966,7 @@
         <v>17.9</v>
       </c>
       <c r="H3">
-        <v>9.1</v>
+        <v>7.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -7998,7 +7998,7 @@
         <v>15.4</v>
       </c>
       <c r="H4">
-        <v>9.199999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -8030,7 +8030,7 @@
         <v>7.7</v>
       </c>
       <c r="H5">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -8062,7 +8062,7 @@
         <v>5.1</v>
       </c>
       <c r="H6">
-        <v>9.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -8094,7 +8094,7 @@
         <v>5.1</v>
       </c>
       <c r="H7">
-        <v>9.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -8126,7 +8126,7 @@
         <v>5.1</v>
       </c>
       <c r="H8">
-        <v>9.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="I8">
         <v>0</v>
